--- a/data/nzd0094/nzd0094.xlsx
+++ b/data/nzd0094/nzd0094.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD248"/>
+  <dimension ref="A1:AD249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24093,6 +24093,102 @@
         </is>
       </c>
     </row>
+    <row r="249">
+      <c r="A249" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>351.71</v>
+      </c>
+      <c r="C249" t="n">
+        <v>360.31</v>
+      </c>
+      <c r="D249" t="n">
+        <v>377.97</v>
+      </c>
+      <c r="E249" t="n">
+        <v>380.92</v>
+      </c>
+      <c r="F249" t="n">
+        <v>375.7</v>
+      </c>
+      <c r="G249" t="n">
+        <v>369.66</v>
+      </c>
+      <c r="H249" t="n">
+        <v>367.22</v>
+      </c>
+      <c r="I249" t="n">
+        <v>360.27</v>
+      </c>
+      <c r="J249" t="n">
+        <v>361.79</v>
+      </c>
+      <c r="K249" t="n">
+        <v>366.16</v>
+      </c>
+      <c r="L249" t="n">
+        <v>370.34</v>
+      </c>
+      <c r="M249" t="n">
+        <v>379.98</v>
+      </c>
+      <c r="N249" t="n">
+        <v>383.75</v>
+      </c>
+      <c r="O249" t="n">
+        <v>378.16</v>
+      </c>
+      <c r="P249" t="n">
+        <v>373.14</v>
+      </c>
+      <c r="Q249" t="n">
+        <v>374.81</v>
+      </c>
+      <c r="R249" t="n">
+        <v>374.23</v>
+      </c>
+      <c r="S249" t="n">
+        <v>384.52</v>
+      </c>
+      <c r="T249" t="n">
+        <v>387</v>
+      </c>
+      <c r="U249" t="n">
+        <v>395.8</v>
+      </c>
+      <c r="V249" t="n">
+        <v>394.51</v>
+      </c>
+      <c r="W249" t="n">
+        <v>395.29</v>
+      </c>
+      <c r="X249" t="n">
+        <v>395.5</v>
+      </c>
+      <c r="Y249" t="n">
+        <v>387.94</v>
+      </c>
+      <c r="Z249" t="n">
+        <v>386.27</v>
+      </c>
+      <c r="AA249" t="n">
+        <v>377.21</v>
+      </c>
+      <c r="AB249" t="n">
+        <v>373.37</v>
+      </c>
+      <c r="AC249" t="n">
+        <v>378.25</v>
+      </c>
+      <c r="AD249" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24104,7 +24200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B251"/>
+  <dimension ref="A1:B252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26617,6 +26713,16 @@
       </c>
       <c r="B251" t="n">
         <v>0.12</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>1.14</v>
       </c>
     </row>
   </sheetData>
@@ -26785,28 +26891,28 @@
         <v>0.0102</v>
       </c>
       <c r="I2" t="n">
-        <v>1.114961605797406</v>
+        <v>1.072083107191889</v>
       </c>
       <c r="J2" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K2" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04540906528286159</v>
+        <v>0.04217588164326724</v>
       </c>
       <c r="M2" t="n">
-        <v>26.74296065111702</v>
+        <v>26.78394671616722</v>
       </c>
       <c r="N2" t="n">
-        <v>1112.294041926248</v>
+        <v>1116.106177976942</v>
       </c>
       <c r="O2" t="n">
-        <v>33.35107257534978</v>
+        <v>33.40817531648416</v>
       </c>
       <c r="P2" t="n">
-        <v>367.3176058797418</v>
+        <v>367.8443129353797</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -26867,28 +26973,28 @@
         <v>0.0104</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9565871264756596</v>
+        <v>0.9125923744683205</v>
       </c>
       <c r="J3" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K3" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05158121312175568</v>
+        <v>0.04697114711614347</v>
       </c>
       <c r="M3" t="n">
-        <v>22.38057890615256</v>
+        <v>22.43783410309172</v>
       </c>
       <c r="N3" t="n">
-        <v>766.3337332671287</v>
+        <v>772.8958216281915</v>
       </c>
       <c r="O3" t="n">
-        <v>27.68273348618465</v>
+        <v>27.80100396798992</v>
       </c>
       <c r="P3" t="n">
-        <v>382.574419051586</v>
+        <v>383.1002275621237</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -26949,28 +27055,28 @@
         <v>0.0106</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3517825888748722</v>
+        <v>0.339777601503213</v>
       </c>
       <c r="J4" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K4" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L4" t="n">
-        <v>0.007667140473856415</v>
+        <v>0.007213828947017054</v>
       </c>
       <c r="M4" t="n">
-        <v>21.53706590888704</v>
+        <v>21.48151019404924</v>
       </c>
       <c r="N4" t="n">
-        <v>690.979080969277</v>
+        <v>688.6625118615193</v>
       </c>
       <c r="O4" t="n">
-        <v>26.28648095446169</v>
+        <v>26.24238007234708</v>
       </c>
       <c r="P4" t="n">
-        <v>381.4118273421847</v>
+        <v>381.5577817722108</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -27031,28 +27137,28 @@
         <v>0.0239</v>
       </c>
       <c r="I5" t="n">
-        <v>0.770457210373188</v>
+        <v>0.7761666466943525</v>
       </c>
       <c r="J5" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K5" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07172659678077331</v>
+        <v>0.07327747969533183</v>
       </c>
       <c r="M5" t="n">
-        <v>15.29966671183991</v>
+        <v>15.26554397683374</v>
       </c>
       <c r="N5" t="n">
-        <v>349.0903831683196</v>
+        <v>347.8283890742173</v>
       </c>
       <c r="O5" t="n">
-        <v>18.68396058570879</v>
+        <v>18.65015788335899</v>
       </c>
       <c r="P5" t="n">
-        <v>354.281570955306</v>
+        <v>354.2147061878298</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27109,28 +27215,28 @@
         <v>0.0308</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2667410884718368</v>
+        <v>0.2778085994403851</v>
       </c>
       <c r="J6" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K6" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01544106012178148</v>
+        <v>0.01682319099265395</v>
       </c>
       <c r="M6" t="n">
-        <v>11.61785137292973</v>
+        <v>11.62412687109735</v>
       </c>
       <c r="N6" t="n">
-        <v>201.0836881521707</v>
+        <v>200.8748240229023</v>
       </c>
       <c r="O6" t="n">
-        <v>14.18039802516737</v>
+        <v>14.17303157489259</v>
       </c>
       <c r="P6" t="n">
-        <v>356.390693488287</v>
+        <v>356.2595250351188</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27187,28 +27293,28 @@
         <v>0.0359</v>
       </c>
       <c r="I7" t="n">
-        <v>0.197377340845128</v>
+        <v>0.2068765994322101</v>
       </c>
       <c r="J7" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K7" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01168912750604933</v>
+        <v>0.01289956060637965</v>
       </c>
       <c r="M7" t="n">
-        <v>10.24497265831308</v>
+        <v>10.2380323315987</v>
       </c>
       <c r="N7" t="n">
-        <v>147.1825023010957</v>
+        <v>147.0398198353429</v>
       </c>
       <c r="O7" t="n">
-        <v>12.13187958649012</v>
+        <v>12.12599768412245</v>
       </c>
       <c r="P7" t="n">
-        <v>353.8389983393823</v>
+        <v>353.7270062174893</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27265,28 +27371,28 @@
         <v>0.0369</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1089914165276719</v>
+        <v>0.1182493825751655</v>
       </c>
       <c r="J8" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K8" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L8" t="n">
-        <v>0.005161056762497673</v>
+        <v>0.006097432885037057</v>
       </c>
       <c r="M8" t="n">
-        <v>8.228753858556347</v>
+        <v>8.230812827668379</v>
       </c>
       <c r="N8" t="n">
-        <v>102.3172487584976</v>
+        <v>102.3340927413386</v>
       </c>
       <c r="O8" t="n">
-        <v>10.1151988986128</v>
+        <v>10.11603147194287</v>
       </c>
       <c r="P8" t="n">
-        <v>353.9799982761203</v>
+        <v>353.8708508881883</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27343,28 +27449,28 @@
         <v>0.0422</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1893980678815556</v>
+        <v>0.1913359216520499</v>
       </c>
       <c r="J9" t="n">
+        <v>248</v>
+      </c>
+      <c r="K9" t="n">
         <v>247</v>
       </c>
-      <c r="K9" t="n">
-        <v>246</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.02252204499370725</v>
+        <v>0.02316747446180167</v>
       </c>
       <c r="M9" t="n">
-        <v>6.761677444703355</v>
+        <v>6.742840407463829</v>
       </c>
       <c r="N9" t="n">
-        <v>70.1227065124129</v>
+        <v>69.85797048158541</v>
       </c>
       <c r="O9" t="n">
-        <v>8.373930171216672</v>
+        <v>8.358108068312195</v>
       </c>
       <c r="P9" t="n">
-        <v>353.1173198649461</v>
+        <v>353.0945926366962</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27421,28 +27527,28 @@
         <v>0.045</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2699686892752836</v>
+        <v>0.2706281886229899</v>
       </c>
       <c r="J10" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K10" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04806971379003155</v>
+        <v>0.04869863725899903</v>
       </c>
       <c r="M10" t="n">
-        <v>6.559006200436</v>
+        <v>6.535591753561294</v>
       </c>
       <c r="N10" t="n">
-        <v>65.10937265166471</v>
+        <v>64.84692716786236</v>
       </c>
       <c r="O10" t="n">
-        <v>8.069037901241058</v>
+        <v>8.052758978627285</v>
       </c>
       <c r="P10" t="n">
-        <v>353.9680573588429</v>
+        <v>353.9603196864774</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27499,28 +27605,28 @@
         <v>0.0478</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3295653812421726</v>
+        <v>0.3307915771901945</v>
       </c>
       <c r="J11" t="n">
+        <v>248</v>
+      </c>
+      <c r="K11" t="n">
         <v>247</v>
       </c>
-      <c r="K11" t="n">
-        <v>246</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.07782741852247033</v>
+        <v>0.07899261164079241</v>
       </c>
       <c r="M11" t="n">
-        <v>6.235129004606151</v>
+        <v>6.216225263082056</v>
       </c>
       <c r="N11" t="n">
-        <v>57.96571306873714</v>
+        <v>57.73870607133406</v>
       </c>
       <c r="O11" t="n">
-        <v>7.613521725767724</v>
+        <v>7.598598954500367</v>
       </c>
       <c r="P11" t="n">
-        <v>356.1396357704164</v>
+        <v>356.1252548942047</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27577,28 +27683,28 @@
         <v>0.0536</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2420233547216101</v>
+        <v>0.2421859981990338</v>
       </c>
       <c r="J12" t="n">
+        <v>248</v>
+      </c>
+      <c r="K12" t="n">
         <v>247</v>
       </c>
-      <c r="K12" t="n">
-        <v>246</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.05645572473403626</v>
+        <v>0.05699995655057655</v>
       </c>
       <c r="M12" t="n">
-        <v>5.283338479985794</v>
+        <v>5.262711969567408</v>
       </c>
       <c r="N12" t="n">
-        <v>44.09377500803625</v>
+        <v>43.91539267809922</v>
       </c>
       <c r="O12" t="n">
-        <v>6.640314375693086</v>
+        <v>6.626868995091062</v>
       </c>
       <c r="P12" t="n">
-        <v>363.8212437325645</v>
+        <v>363.8193362432115</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -27655,28 +27761,28 @@
         <v>0.0468</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2313258684514765</v>
+        <v>0.2328540742120072</v>
       </c>
       <c r="J13" t="n">
+        <v>248</v>
+      </c>
+      <c r="K13" t="n">
         <v>247</v>
       </c>
-      <c r="K13" t="n">
-        <v>246</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.05437465218311055</v>
+        <v>0.05550200693020435</v>
       </c>
       <c r="M13" t="n">
-        <v>5.350349657768334</v>
+        <v>5.336605115002599</v>
       </c>
       <c r="N13" t="n">
-        <v>41.91596291785024</v>
+        <v>41.75817927153572</v>
       </c>
       <c r="O13" t="n">
-        <v>6.474253850278829</v>
+        <v>6.462056891697544</v>
       </c>
       <c r="P13" t="n">
-        <v>372.1918521537431</v>
+        <v>372.1739292941025</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -27733,28 +27839,28 @@
         <v>0.0508</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1364067085616921</v>
+        <v>0.1347395961786851</v>
       </c>
       <c r="J14" t="n">
+        <v>248</v>
+      </c>
+      <c r="K14" t="n">
         <v>247</v>
       </c>
-      <c r="K14" t="n">
-        <v>246</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.02446902512333604</v>
+        <v>0.0240855337967254</v>
       </c>
       <c r="M14" t="n">
-        <v>4.763009113813557</v>
+        <v>4.750726271584942</v>
       </c>
       <c r="N14" t="n">
-        <v>33.41213964501826</v>
+        <v>33.29104921321198</v>
       </c>
       <c r="O14" t="n">
-        <v>5.780323489651619</v>
+        <v>5.769839617633404</v>
       </c>
       <c r="P14" t="n">
-        <v>382.0620659480155</v>
+        <v>382.0816179102036</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -27811,28 +27917,28 @@
         <v>0.0555</v>
       </c>
       <c r="I15" t="n">
-        <v>0.12807653521725</v>
+        <v>0.1263680598314216</v>
       </c>
       <c r="J15" t="n">
+        <v>248</v>
+      </c>
+      <c r="K15" t="n">
         <v>247</v>
       </c>
-      <c r="K15" t="n">
-        <v>246</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.0211776591646059</v>
+        <v>0.02079823839403927</v>
       </c>
       <c r="M15" t="n">
-        <v>4.778883920332402</v>
+        <v>4.766944605355143</v>
       </c>
       <c r="N15" t="n">
-        <v>34.14864621094254</v>
+        <v>34.02528641474152</v>
       </c>
       <c r="O15" t="n">
-        <v>5.843684301101706</v>
+        <v>5.83311978402137</v>
       </c>
       <c r="P15" t="n">
-        <v>376.7386840090648</v>
+        <v>376.7587210782411</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -27889,28 +27995,28 @@
         <v>0.0487</v>
       </c>
       <c r="I16" t="n">
-        <v>0.02714029709231484</v>
+        <v>0.02287281152728085</v>
       </c>
       <c r="J16" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K16" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L16" t="n">
-        <v>0.000777828041865769</v>
+        <v>0.0005562393306945967</v>
       </c>
       <c r="M16" t="n">
-        <v>5.402817108339937</v>
+        <v>5.398689454041757</v>
       </c>
       <c r="N16" t="n">
-        <v>42.68794174210016</v>
+        <v>42.6070340438718</v>
       </c>
       <c r="O16" t="n">
-        <v>6.533600978181952</v>
+        <v>6.527406379556263</v>
       </c>
       <c r="P16" t="n">
-        <v>377.2400986179176</v>
+        <v>377.2902240221971</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -27967,28 +28073,28 @@
         <v>0.0534</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0383064516986269</v>
+        <v>0.03698803122705589</v>
       </c>
       <c r="J17" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K17" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L17" t="n">
-        <v>0.001459006461918433</v>
+        <v>0.001372183080519673</v>
       </c>
       <c r="M17" t="n">
-        <v>5.312038540755626</v>
+        <v>5.295845663252936</v>
       </c>
       <c r="N17" t="n">
-        <v>45.3054124768767</v>
+        <v>45.12940040998155</v>
       </c>
       <c r="O17" t="n">
-        <v>6.730929540329234</v>
+        <v>6.717841945891668</v>
       </c>
       <c r="P17" t="n">
-        <v>375.2900702109388</v>
+        <v>375.3055562291432</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -28045,28 +28151,28 @@
         <v>0.0579</v>
       </c>
       <c r="I18" t="n">
-        <v>0.07015583830138514</v>
+        <v>0.06717179993196302</v>
       </c>
       <c r="J18" t="n">
+        <v>248</v>
+      </c>
+      <c r="K18" t="n">
         <v>247</v>
       </c>
-      <c r="K18" t="n">
-        <v>246</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.005521030757117185</v>
+        <v>0.005102561596560085</v>
       </c>
       <c r="M18" t="n">
-        <v>5.22144728168433</v>
+        <v>5.212150992928019</v>
       </c>
       <c r="N18" t="n">
-        <v>39.93112126564093</v>
+        <v>39.81489256842751</v>
       </c>
       <c r="O18" t="n">
-        <v>6.319107632066488</v>
+        <v>6.309904323238785</v>
       </c>
       <c r="P18" t="n">
-        <v>375.7655569341979</v>
+        <v>375.8005538581976</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -28123,28 +28229,28 @@
         <v>0.053</v>
       </c>
       <c r="I19" t="n">
-        <v>0.09024996651784443</v>
+        <v>0.09239934170993422</v>
       </c>
       <c r="J19" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K19" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L19" t="n">
-        <v>0.008232763630101392</v>
+        <v>0.00869717525266489</v>
       </c>
       <c r="M19" t="n">
-        <v>5.446319682538558</v>
+        <v>5.435358886513667</v>
       </c>
       <c r="N19" t="n">
-        <v>44.54175170313982</v>
+        <v>44.38596521815742</v>
       </c>
       <c r="O19" t="n">
-        <v>6.673960720826863</v>
+        <v>6.662279281008671</v>
       </c>
       <c r="P19" t="n">
-        <v>379.708132214399</v>
+        <v>379.6830552764029</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -28201,28 +28307,28 @@
         <v>0.049</v>
       </c>
       <c r="I20" t="n">
-        <v>0.06706513815337151</v>
+        <v>0.06742587187319746</v>
       </c>
       <c r="J20" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K20" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0046231018485271</v>
+        <v>0.004714128134405082</v>
       </c>
       <c r="M20" t="n">
-        <v>5.183151483883957</v>
+        <v>5.163824949082701</v>
       </c>
       <c r="N20" t="n">
-        <v>42.92201885168545</v>
+        <v>42.74747698357658</v>
       </c>
       <c r="O20" t="n">
-        <v>6.551489819246112</v>
+        <v>6.538155472576082</v>
       </c>
       <c r="P20" t="n">
-        <v>384.8448403436537</v>
+        <v>384.8405650477747</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -28279,28 +28385,28 @@
         <v>0.0506</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1913812251026026</v>
+        <v>0.1935260143271678</v>
       </c>
       <c r="J21" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K21" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L21" t="n">
-        <v>0.03775711493904366</v>
+        <v>0.03888408125693732</v>
       </c>
       <c r="M21" t="n">
-        <v>4.963452640572899</v>
+        <v>4.955055272902015</v>
       </c>
       <c r="N21" t="n">
-        <v>41.7094713150142</v>
+        <v>41.56314761051564</v>
       </c>
       <c r="O21" t="n">
-        <v>6.45828702637272</v>
+        <v>6.446948705435435</v>
       </c>
       <c r="P21" t="n">
-        <v>388.3824276902673</v>
+        <v>388.3571415593477</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -28357,28 +28463,28 @@
         <v>0.057</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1292520768157726</v>
+        <v>0.1323254115028098</v>
       </c>
       <c r="J22" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K22" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L22" t="n">
-        <v>0.02258054110180718</v>
+        <v>0.02381100867161123</v>
       </c>
       <c r="M22" t="n">
-        <v>4.365549801312982</v>
+        <v>4.364614383272921</v>
       </c>
       <c r="N22" t="n">
-        <v>32.82696858257151</v>
+        <v>32.74329726330893</v>
       </c>
       <c r="O22" t="n">
-        <v>5.729482400930428</v>
+        <v>5.722175920339127</v>
       </c>
       <c r="P22" t="n">
-        <v>387.6299567492314</v>
+        <v>387.5940998994494</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -28435,28 +28541,28 @@
         <v>0.0611</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1642805709840007</v>
+        <v>0.168965352635555</v>
       </c>
       <c r="J23" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K23" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L23" t="n">
-        <v>0.03534556808260481</v>
+        <v>0.03750897025908528</v>
       </c>
       <c r="M23" t="n">
-        <v>4.384298921100286</v>
+        <v>4.389527782430798</v>
       </c>
       <c r="N23" t="n">
-        <v>33.43630578965509</v>
+        <v>33.41463019673871</v>
       </c>
       <c r="O23" t="n">
-        <v>5.782413491757148</v>
+        <v>5.780538919230517</v>
       </c>
       <c r="P23" t="n">
-        <v>385.6551643710113</v>
+        <v>385.6005066363203</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -28513,28 +28619,28 @@
         <v>0.064</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2192767828132317</v>
+        <v>0.2241984364503729</v>
       </c>
       <c r="J24" t="n">
+        <v>248</v>
+      </c>
+      <c r="K24" t="n">
         <v>247</v>
       </c>
-      <c r="K24" t="n">
-        <v>246</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.05177490361488957</v>
+        <v>0.05428784630155437</v>
       </c>
       <c r="M24" t="n">
-        <v>4.986507252511925</v>
+        <v>4.987981539000223</v>
       </c>
       <c r="N24" t="n">
-        <v>40.03926513510552</v>
+        <v>40.0024686842758</v>
       </c>
       <c r="O24" t="n">
-        <v>6.327658740411458</v>
+        <v>6.324750483953956</v>
       </c>
       <c r="P24" t="n">
-        <v>384.1583673225319</v>
+        <v>384.1009253785767</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -28591,28 +28697,28 @@
         <v>0.0766</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1615221029699389</v>
+        <v>0.166466247706134</v>
       </c>
       <c r="J25" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K25" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L25" t="n">
-        <v>0.04241006455588758</v>
+        <v>0.04510341912967364</v>
       </c>
       <c r="M25" t="n">
-        <v>4.096206855603695</v>
+        <v>4.100508413919146</v>
       </c>
       <c r="N25" t="n">
-        <v>26.74136940313705</v>
+        <v>26.75956475306477</v>
       </c>
       <c r="O25" t="n">
-        <v>5.17120579779388</v>
+        <v>5.172964793333198</v>
       </c>
       <c r="P25" t="n">
-        <v>378.0839304502882</v>
+        <v>378.0262467050542</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -28669,28 +28775,28 @@
         <v>0.0496</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1158258830907404</v>
+        <v>0.1156752140731335</v>
       </c>
       <c r="J26" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K26" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L26" t="n">
-        <v>0.01619967627616947</v>
+        <v>0.01629881422594348</v>
       </c>
       <c r="M26" t="n">
-        <v>4.577600483897225</v>
+        <v>4.559768017618133</v>
       </c>
       <c r="N26" t="n">
-        <v>36.98460192428579</v>
+        <v>36.8355875002302</v>
       </c>
       <c r="O26" t="n">
-        <v>6.081496684557658</v>
+        <v>6.069232859285447</v>
       </c>
       <c r="P26" t="n">
-        <v>383.4073179575884</v>
+        <v>383.4090758254684</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -28747,28 +28853,28 @@
         <v>0.0752</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1432790649400987</v>
+        <v>0.1485308942564028</v>
       </c>
       <c r="J27" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K27" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L27" t="n">
-        <v>0.03630925790854655</v>
+        <v>0.0390286905856102</v>
       </c>
       <c r="M27" t="n">
-        <v>3.757976416745563</v>
+        <v>3.76911588558261</v>
       </c>
       <c r="N27" t="n">
-        <v>24.73402950261015</v>
+        <v>24.77649244498052</v>
       </c>
       <c r="O27" t="n">
-        <v>4.97333183113797</v>
+        <v>4.977599064306055</v>
       </c>
       <c r="P27" t="n">
-        <v>367.4766689895113</v>
+        <v>367.4153954628533</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -28825,28 +28931,28 @@
         <v>0.0784</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1243563860595649</v>
+        <v>0.1297422855334443</v>
       </c>
       <c r="J28" t="n">
+        <v>248</v>
+      </c>
+      <c r="K28" t="n">
         <v>247</v>
       </c>
-      <c r="K28" t="n">
-        <v>246</v>
-      </c>
       <c r="L28" t="n">
-        <v>0.02038132674698101</v>
+        <v>0.02223955231563968</v>
       </c>
       <c r="M28" t="n">
-        <v>4.508219280725227</v>
+        <v>4.512552136638153</v>
       </c>
       <c r="N28" t="n">
-        <v>33.70235531471652</v>
+        <v>33.71543051624429</v>
       </c>
       <c r="O28" t="n">
-        <v>5.805372969475477</v>
+        <v>5.80649898960159</v>
       </c>
       <c r="P28" t="n">
-        <v>363.9977016540091</v>
+        <v>363.9347443927202</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -28903,28 +29009,28 @@
         <v>0.1741</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.01801025577388138</v>
+        <v>-0.01230559193445348</v>
       </c>
       <c r="J29" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K29" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L29" t="n">
-        <v>0.0005686023404556373</v>
+        <v>0.000266130503674411</v>
       </c>
       <c r="M29" t="n">
-        <v>3.860637535740496</v>
+        <v>3.866674435794519</v>
       </c>
       <c r="N29" t="n">
-        <v>25.9264564775874</v>
+        <v>25.98959501651427</v>
       </c>
       <c r="O29" t="n">
-        <v>5.091802871045521</v>
+        <v>5.097999118920507</v>
       </c>
       <c r="P29" t="n">
-        <v>372.2447697778114</v>
+        <v>372.1781165372801</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -28962,7 +29068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD248"/>
+  <dimension ref="A1:AD249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66257,6 +66363,158 @@
         </is>
       </c>
     </row>
+    <row r="249">
+      <c r="A249" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>-35.63188640811581,174.51485466600744</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>-35.63257189476763,174.5145334402675</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>-35.633293546826984,174.51430190937972</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>-35.63397250650978,174.51391517956841</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>-35.63452325176146,174.51329195262286</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>-35.63501760219586,174.5126190693496</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>-35.635530352858886,174.51197868217102</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>-35.63601535037043,174.51130183093332</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>-35.63655627055399,174.51069835128345</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>-35.637115728467684,174.51011979359313</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>-35.63767402991746,174.5095397064706</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>-35.63826262015863,174.50900690488913</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>-35.63881752732862,174.50847605545397</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>-35.639418744317986,174.50800645224018</t>
+        </is>
+      </c>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>-35.64004021298566,174.50753088943912</t>
+        </is>
+      </c>
+      <c r="Q249" t="inlineStr">
+        <is>
+          <t>-35.64069111337018,174.50711999657975</t>
+        </is>
+      </c>
+      <c r="R249" t="inlineStr">
+        <is>
+          <t>-35.641323914841465,174.50666580839794</t>
+        </is>
+      </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>-35.64199676807056,174.50629787125797</t>
+        </is>
+      </c>
+      <c r="T249" t="inlineStr">
+        <is>
+          <t>-35.642632692981124,174.50585631293316</t>
+        </is>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>-35.64328643066512,174.50548196593297</t>
+        </is>
+      </c>
+      <c r="V249" t="inlineStr">
+        <is>
+          <t>-35.643920262739194,174.5050784820739</t>
+        </is>
+      </c>
+      <c r="W249" t="inlineStr">
+        <is>
+          <t>-35.64458137560516,174.50470732438532</t>
+        </is>
+      </c>
+      <c r="X249" t="inlineStr">
+        <is>
+          <t>-35.645228701724584,174.50433584480336</t>
+        </is>
+      </c>
+      <c r="Y249" t="inlineStr">
+        <is>
+          <t>-35.64588062184467,174.50397110265038</t>
+        </is>
+      </c>
+      <c r="Z249" t="inlineStr">
+        <is>
+          <t>-35.646567901657434,174.5036726006251</t>
+        </is>
+      </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>-35.647236370260586,174.50329584413186</t>
+        </is>
+      </c>
+      <c r="AB249" t="inlineStr">
+        <is>
+          <t>-35.64791333097496,174.5029754361229</t>
+        </is>
+      </c>
+      <c r="AC249" t="inlineStr">
+        <is>
+          <t>-35.64862758975786,174.50285325122653</t>
+        </is>
+      </c>
+      <c r="AD249" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0094/nzd0094.xlsx
+++ b/data/nzd0094/nzd0094.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD249"/>
+  <dimension ref="A1:AD250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24100,10 +24100,10 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>351.71</v>
+        <v>361.39</v>
       </c>
       <c r="C249" t="n">
-        <v>360.31</v>
+        <v>373.99</v>
       </c>
       <c r="D249" t="n">
         <v>377.97</v>
@@ -24184,6 +24184,102 @@
         <v>378.25</v>
       </c>
       <c r="AD249" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>361.29</v>
+      </c>
+      <c r="C250" t="n">
+        <v>375.48</v>
+      </c>
+      <c r="D250" t="n">
+        <v>382.78</v>
+      </c>
+      <c r="E250" t="n">
+        <v>382.79</v>
+      </c>
+      <c r="F250" t="n">
+        <v>377.84</v>
+      </c>
+      <c r="G250" t="n">
+        <v>372.17</v>
+      </c>
+      <c r="H250" t="n">
+        <v>368.84</v>
+      </c>
+      <c r="I250" t="n">
+        <v>362.83</v>
+      </c>
+      <c r="J250" t="n">
+        <v>363.35</v>
+      </c>
+      <c r="K250" t="n">
+        <v>367.2</v>
+      </c>
+      <c r="L250" t="n">
+        <v>371.01</v>
+      </c>
+      <c r="M250" t="n">
+        <v>379.51</v>
+      </c>
+      <c r="N250" t="n">
+        <v>384.21</v>
+      </c>
+      <c r="O250" t="n">
+        <v>377.48</v>
+      </c>
+      <c r="P250" t="n">
+        <v>373.48</v>
+      </c>
+      <c r="Q250" t="n">
+        <v>375.14</v>
+      </c>
+      <c r="R250" t="n">
+        <v>375.12</v>
+      </c>
+      <c r="S250" t="n">
+        <v>383.72</v>
+      </c>
+      <c r="T250" t="n">
+        <v>388.41</v>
+      </c>
+      <c r="U250" t="n">
+        <v>395.26</v>
+      </c>
+      <c r="V250" t="n">
+        <v>395.33</v>
+      </c>
+      <c r="W250" t="n">
+        <v>395.48</v>
+      </c>
+      <c r="X250" t="n">
+        <v>396.28</v>
+      </c>
+      <c r="Y250" t="n">
+        <v>387.99</v>
+      </c>
+      <c r="Z250" t="n">
+        <v>388.21</v>
+      </c>
+      <c r="AA250" t="n">
+        <v>377.65</v>
+      </c>
+      <c r="AB250" t="n">
+        <v>375.09</v>
+      </c>
+      <c r="AC250" t="n">
+        <v>378.19</v>
+      </c>
+      <c r="AD250" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -24200,7 +24296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B252"/>
+  <dimension ref="A1:B253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26723,6 +26819,16 @@
       </c>
       <c r="B252" t="n">
         <v>1.14</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>0.73</v>
       </c>
     </row>
   </sheetData>
@@ -26891,28 +26997,28 @@
         <v>0.0102</v>
       </c>
       <c r="I2" t="n">
-        <v>1.072083107191889</v>
+        <v>1.04812396942221</v>
       </c>
       <c r="J2" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K2" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04217588164326724</v>
+        <v>0.04067112637585502</v>
       </c>
       <c r="M2" t="n">
-        <v>26.78394671616722</v>
+        <v>26.75447718800512</v>
       </c>
       <c r="N2" t="n">
-        <v>1116.106177976942</v>
+        <v>1113.134207488573</v>
       </c>
       <c r="O2" t="n">
-        <v>33.40817531648416</v>
+        <v>33.36366597795531</v>
       </c>
       <c r="P2" t="n">
-        <v>367.8443129353797</v>
+        <v>368.1400370200131</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -26973,28 +27079,28 @@
         <v>0.0104</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9125923744683205</v>
+        <v>0.8958762362542226</v>
       </c>
       <c r="J3" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K3" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04697114711614347</v>
+        <v>0.04574971643703163</v>
       </c>
       <c r="M3" t="n">
-        <v>22.43783410309172</v>
+        <v>22.39742786989591</v>
       </c>
       <c r="N3" t="n">
-        <v>772.8958216281915</v>
+        <v>768.9646605899472</v>
       </c>
       <c r="O3" t="n">
-        <v>27.80100396798992</v>
+        <v>27.73021205454346</v>
       </c>
       <c r="P3" t="n">
-        <v>383.1002275621237</v>
+        <v>383.301347976467</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -27055,28 +27161,28 @@
         <v>0.0106</v>
       </c>
       <c r="I4" t="n">
-        <v>0.339777601503213</v>
+        <v>0.3325009780912476</v>
       </c>
       <c r="J4" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K4" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L4" t="n">
-        <v>0.007213828947017054</v>
+        <v>0.006970085829648198</v>
       </c>
       <c r="M4" t="n">
-        <v>21.48151019404924</v>
+        <v>21.41122991253868</v>
       </c>
       <c r="N4" t="n">
-        <v>688.6625118615193</v>
+        <v>685.9349556779833</v>
       </c>
       <c r="O4" t="n">
-        <v>26.24238007234708</v>
+        <v>26.19035997610539</v>
       </c>
       <c r="P4" t="n">
-        <v>381.5577817722108</v>
+        <v>381.6465560410489</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -27137,28 +27243,28 @@
         <v>0.0239</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7761666466943525</v>
+        <v>0.783365744425969</v>
       </c>
       <c r="J5" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K5" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07327747969533183</v>
+        <v>0.0750959106647977</v>
       </c>
       <c r="M5" t="n">
-        <v>15.26554397683374</v>
+        <v>15.23899129610336</v>
       </c>
       <c r="N5" t="n">
-        <v>347.8283890742173</v>
+        <v>346.6779701721783</v>
       </c>
       <c r="O5" t="n">
-        <v>18.65015788335899</v>
+        <v>18.61929027036687</v>
       </c>
       <c r="P5" t="n">
-        <v>354.2147061878298</v>
+        <v>354.1301013749131</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27215,28 +27321,28 @@
         <v>0.0308</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2778085994403851</v>
+        <v>0.2905757109288102</v>
       </c>
       <c r="J6" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K6" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01682319099265395</v>
+        <v>0.01846278846981286</v>
       </c>
       <c r="M6" t="n">
-        <v>11.62412687109735</v>
+        <v>11.63867780570443</v>
       </c>
       <c r="N6" t="n">
-        <v>200.8748240229023</v>
+        <v>200.8758074227886</v>
       </c>
       <c r="O6" t="n">
-        <v>14.17303157489259</v>
+        <v>14.17306626749443</v>
       </c>
       <c r="P6" t="n">
-        <v>356.2595250351188</v>
+        <v>356.1076993075171</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27293,28 +27399,28 @@
         <v>0.0359</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2068765994322101</v>
+        <v>0.2184283610396531</v>
       </c>
       <c r="J7" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K7" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01289956060637965</v>
+        <v>0.01441938910736063</v>
       </c>
       <c r="M7" t="n">
-        <v>10.2380323315987</v>
+        <v>10.23822761456857</v>
       </c>
       <c r="N7" t="n">
-        <v>147.0398198353429</v>
+        <v>147.1210468413169</v>
       </c>
       <c r="O7" t="n">
-        <v>12.12599768412245</v>
+        <v>12.12934651336653</v>
       </c>
       <c r="P7" t="n">
-        <v>353.7270062174893</v>
+        <v>353.5903514236348</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27371,28 +27477,28 @@
         <v>0.0369</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1182493825751655</v>
+        <v>0.1287850402835656</v>
       </c>
       <c r="J8" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K8" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L8" t="n">
-        <v>0.006097432885037057</v>
+        <v>0.007248249117714045</v>
       </c>
       <c r="M8" t="n">
-        <v>8.230812827668379</v>
+        <v>8.238937664912342</v>
       </c>
       <c r="N8" t="n">
-        <v>102.3340927413386</v>
+        <v>102.4825325667332</v>
       </c>
       <c r="O8" t="n">
-        <v>10.11603147194287</v>
+        <v>10.12336567386228</v>
       </c>
       <c r="P8" t="n">
-        <v>353.8708508881883</v>
+        <v>353.7462163795142</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27449,28 +27555,28 @@
         <v>0.0422</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1913359216520499</v>
+        <v>0.1954829348066763</v>
       </c>
       <c r="J9" t="n">
+        <v>249</v>
+      </c>
+      <c r="K9" t="n">
         <v>248</v>
       </c>
-      <c r="K9" t="n">
-        <v>247</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.02316747446180167</v>
+        <v>0.02433722052410514</v>
       </c>
       <c r="M9" t="n">
-        <v>6.742840407463829</v>
+        <v>6.73367902858859</v>
       </c>
       <c r="N9" t="n">
-        <v>69.85797048158541</v>
+        <v>69.66439733626605</v>
       </c>
       <c r="O9" t="n">
-        <v>8.358108068312195</v>
+        <v>8.346520073435759</v>
       </c>
       <c r="P9" t="n">
-        <v>353.0945926366962</v>
+        <v>353.0457897741736</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27527,28 +27633,28 @@
         <v>0.045</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2706281886229899</v>
+        <v>0.2726371528491806</v>
       </c>
       <c r="J10" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K10" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04869863725899903</v>
+        <v>0.04978906397703975</v>
       </c>
       <c r="M10" t="n">
-        <v>6.535591753561294</v>
+        <v>6.518898357859396</v>
       </c>
       <c r="N10" t="n">
-        <v>64.84692716786236</v>
+        <v>64.6051353907951</v>
       </c>
       <c r="O10" t="n">
-        <v>8.052758978627285</v>
+        <v>8.037731980527536</v>
       </c>
       <c r="P10" t="n">
-        <v>353.9603196864774</v>
+        <v>353.9366680758432</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27605,28 +27711,28 @@
         <v>0.0478</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3307915771901945</v>
+        <v>0.3328883254157755</v>
       </c>
       <c r="J11" t="n">
+        <v>249</v>
+      </c>
+      <c r="K11" t="n">
         <v>248</v>
       </c>
-      <c r="K11" t="n">
-        <v>247</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.07899261164079241</v>
+        <v>0.08054006330557106</v>
       </c>
       <c r="M11" t="n">
-        <v>6.216225263082056</v>
+        <v>6.201861026481155</v>
       </c>
       <c r="N11" t="n">
-        <v>57.73870607133406</v>
+        <v>57.5284133494354</v>
       </c>
       <c r="O11" t="n">
-        <v>7.598598954500367</v>
+        <v>7.584748733441036</v>
       </c>
       <c r="P11" t="n">
-        <v>356.1252548942047</v>
+        <v>356.1005799506773</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27683,28 +27789,28 @@
         <v>0.0536</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2421859981990338</v>
+        <v>0.2429118978436709</v>
       </c>
       <c r="J12" t="n">
+        <v>249</v>
+      </c>
+      <c r="K12" t="n">
         <v>248</v>
       </c>
-      <c r="K12" t="n">
-        <v>247</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.05699995655057655</v>
+        <v>0.05779854671811635</v>
       </c>
       <c r="M12" t="n">
-        <v>5.262711969567408</v>
+        <v>5.244855236948338</v>
       </c>
       <c r="N12" t="n">
-        <v>43.91539267809922</v>
+        <v>43.74101420031785</v>
       </c>
       <c r="O12" t="n">
-        <v>6.626868995091062</v>
+        <v>6.613698980171221</v>
       </c>
       <c r="P12" t="n">
-        <v>363.8193362432115</v>
+        <v>363.8107937141089</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -27761,28 +27867,28 @@
         <v>0.0468</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2328540742120072</v>
+        <v>0.23392286897527</v>
       </c>
       <c r="J13" t="n">
+        <v>249</v>
+      </c>
+      <c r="K13" t="n">
         <v>248</v>
       </c>
-      <c r="K13" t="n">
-        <v>247</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.05550200693020435</v>
+        <v>0.05644544046810995</v>
       </c>
       <c r="M13" t="n">
-        <v>5.336605115002599</v>
+        <v>5.320556754989881</v>
       </c>
       <c r="N13" t="n">
-        <v>41.75817927153572</v>
+        <v>41.59565218522744</v>
       </c>
       <c r="O13" t="n">
-        <v>6.462056891697544</v>
+        <v>6.449469139799604</v>
       </c>
       <c r="P13" t="n">
-        <v>372.1739292941025</v>
+        <v>372.161351508127</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -27839,28 +27945,28 @@
         <v>0.0508</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1347395961786851</v>
+        <v>0.1334970273525931</v>
       </c>
       <c r="J14" t="n">
+        <v>249</v>
+      </c>
+      <c r="K14" t="n">
         <v>248</v>
       </c>
-      <c r="K14" t="n">
-        <v>247</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.0240855337967254</v>
+        <v>0.02385318618060039</v>
       </c>
       <c r="M14" t="n">
-        <v>4.750726271584942</v>
+        <v>4.736719031951032</v>
       </c>
       <c r="N14" t="n">
-        <v>33.29104921321198</v>
+        <v>33.16472165321639</v>
       </c>
       <c r="O14" t="n">
-        <v>5.769839617633404</v>
+        <v>5.758881979448475</v>
       </c>
       <c r="P14" t="n">
-        <v>382.0816179102036</v>
+        <v>382.0962407033642</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -27917,28 +28023,28 @@
         <v>0.0555</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1263680598314216</v>
+        <v>0.1240776838801887</v>
       </c>
       <c r="J15" t="n">
+        <v>249</v>
+      </c>
+      <c r="K15" t="n">
         <v>248</v>
       </c>
-      <c r="K15" t="n">
-        <v>247</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.02079823839403927</v>
+        <v>0.02022491948005833</v>
       </c>
       <c r="M15" t="n">
-        <v>4.766944605355143</v>
+        <v>4.757526411495925</v>
       </c>
       <c r="N15" t="n">
-        <v>34.02528641474152</v>
+        <v>33.91496455999522</v>
       </c>
       <c r="O15" t="n">
-        <v>5.83311978402137</v>
+        <v>5.823655601080409</v>
       </c>
       <c r="P15" t="n">
-        <v>376.7587210782411</v>
+        <v>376.785674670744</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -27995,28 +28101,28 @@
         <v>0.0487</v>
       </c>
       <c r="I16" t="n">
-        <v>0.02287281152728085</v>
+        <v>0.01897985211326518</v>
       </c>
       <c r="J16" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K16" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0005562393306945967</v>
+        <v>0.0003857554474476776</v>
       </c>
       <c r="M16" t="n">
-        <v>5.398689454041757</v>
+        <v>5.393241246098358</v>
       </c>
       <c r="N16" t="n">
-        <v>42.6070340438718</v>
+        <v>42.5118114103389</v>
       </c>
       <c r="O16" t="n">
-        <v>6.527406379556263</v>
+        <v>6.520108236090786</v>
       </c>
       <c r="P16" t="n">
-        <v>377.2902240221971</v>
+        <v>377.3361083194411</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -28073,28 +28179,28 @@
         <v>0.0534</v>
       </c>
       <c r="I17" t="n">
-        <v>0.03698803122705589</v>
+        <v>0.035980310505958</v>
       </c>
       <c r="J17" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K17" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L17" t="n">
-        <v>0.001372183080519673</v>
+        <v>0.001309854773239083</v>
       </c>
       <c r="M17" t="n">
-        <v>5.295845663252936</v>
+        <v>5.278456262295775</v>
       </c>
       <c r="N17" t="n">
-        <v>45.12940040998155</v>
+        <v>44.95117255240465</v>
       </c>
       <c r="O17" t="n">
-        <v>6.717841945891668</v>
+        <v>6.704563561664894</v>
       </c>
       <c r="P17" t="n">
-        <v>375.3055562291432</v>
+        <v>375.31743371159</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -28151,28 +28257,28 @@
         <v>0.0579</v>
       </c>
       <c r="I18" t="n">
-        <v>0.06717179993196302</v>
+        <v>0.06501720557101413</v>
       </c>
       <c r="J18" t="n">
+        <v>249</v>
+      </c>
+      <c r="K18" t="n">
         <v>248</v>
       </c>
-      <c r="K18" t="n">
-        <v>247</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.005102561596560085</v>
+        <v>0.004821374100300257</v>
       </c>
       <c r="M18" t="n">
-        <v>5.212150992928019</v>
+        <v>5.19957147654061</v>
       </c>
       <c r="N18" t="n">
-        <v>39.81489256842751</v>
+        <v>39.67813327421314</v>
       </c>
       <c r="O18" t="n">
-        <v>6.309904323238785</v>
+        <v>6.299058125959241</v>
       </c>
       <c r="P18" t="n">
-        <v>375.8005538581976</v>
+        <v>375.8259095463685</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -28229,28 +28335,28 @@
         <v>0.053</v>
       </c>
       <c r="I19" t="n">
-        <v>0.09239934170993422</v>
+        <v>0.09381129846239596</v>
       </c>
       <c r="J19" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K19" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L19" t="n">
-        <v>0.00869717525266489</v>
+        <v>0.009039149286562354</v>
       </c>
       <c r="M19" t="n">
-        <v>5.435358886513667</v>
+        <v>5.420667727077299</v>
       </c>
       <c r="N19" t="n">
-        <v>44.38596521815742</v>
+        <v>44.21802875737234</v>
       </c>
       <c r="O19" t="n">
-        <v>6.662279281008671</v>
+        <v>6.649663807845652</v>
       </c>
       <c r="P19" t="n">
-        <v>379.6830552764029</v>
+        <v>379.6665252509939</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -28307,28 +28413,28 @@
         <v>0.049</v>
       </c>
       <c r="I20" t="n">
-        <v>0.06742587187319746</v>
+        <v>0.0690334242343717</v>
       </c>
       <c r="J20" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K20" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L20" t="n">
-        <v>0.004714128134405082</v>
+        <v>0.004982821020412143</v>
       </c>
       <c r="M20" t="n">
-        <v>5.163824949082701</v>
+        <v>5.150882649848843</v>
       </c>
       <c r="N20" t="n">
-        <v>42.74747698357658</v>
+        <v>42.5866683356174</v>
       </c>
       <c r="O20" t="n">
-        <v>6.538155472576082</v>
+        <v>6.525846177747174</v>
       </c>
       <c r="P20" t="n">
-        <v>384.8405650477747</v>
+        <v>384.8214481310692</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -28385,28 +28491,28 @@
         <v>0.0506</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1935260143271678</v>
+        <v>0.1951386989316932</v>
       </c>
       <c r="J21" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K21" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L21" t="n">
-        <v>0.03888408125693732</v>
+        <v>0.03983450921865872</v>
       </c>
       <c r="M21" t="n">
-        <v>4.955055272902015</v>
+        <v>4.943743447776376</v>
       </c>
       <c r="N21" t="n">
-        <v>41.56314761051564</v>
+        <v>41.40806104075629</v>
       </c>
       <c r="O21" t="n">
-        <v>6.446948705435435</v>
+        <v>6.434909559640779</v>
       </c>
       <c r="P21" t="n">
-        <v>388.3571415593477</v>
+        <v>388.3380638559054</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -28463,28 +28569,28 @@
         <v>0.057</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1323254115028098</v>
+        <v>0.1360517717798947</v>
       </c>
       <c r="J22" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K22" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L22" t="n">
-        <v>0.02381100867161123</v>
+        <v>0.02529932051921135</v>
       </c>
       <c r="M22" t="n">
-        <v>4.364614383272921</v>
+        <v>4.367042206729914</v>
       </c>
       <c r="N22" t="n">
-        <v>32.74329726330893</v>
+        <v>32.68368081157595</v>
       </c>
       <c r="O22" t="n">
-        <v>5.722175920339127</v>
+        <v>5.71696430035871</v>
       </c>
       <c r="P22" t="n">
-        <v>387.5940998994494</v>
+        <v>387.5504747459482</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -28541,28 +28647,28 @@
         <v>0.0611</v>
       </c>
       <c r="I23" t="n">
-        <v>0.168965352635555</v>
+        <v>0.1737248967232835</v>
       </c>
       <c r="J23" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K23" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L23" t="n">
-        <v>0.03750897025908528</v>
+        <v>0.03976888595703776</v>
       </c>
       <c r="M23" t="n">
-        <v>4.389527782430798</v>
+        <v>4.396120064846692</v>
       </c>
       <c r="N23" t="n">
-        <v>33.41463019673871</v>
+        <v>33.3977045401545</v>
       </c>
       <c r="O23" t="n">
-        <v>5.780538919230517</v>
+        <v>5.77907471314868</v>
       </c>
       <c r="P23" t="n">
-        <v>385.6005066363203</v>
+        <v>385.5447858186903</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -28619,28 +28725,28 @@
         <v>0.064</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2241984364503729</v>
+        <v>0.2296974602044319</v>
       </c>
       <c r="J24" t="n">
+        <v>249</v>
+      </c>
+      <c r="K24" t="n">
         <v>248</v>
       </c>
-      <c r="K24" t="n">
-        <v>247</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.05428784630155437</v>
+        <v>0.05709166599021309</v>
       </c>
       <c r="M24" t="n">
-        <v>4.987981539000223</v>
+        <v>4.99185328073851</v>
       </c>
       <c r="N24" t="n">
-        <v>40.0024686842758</v>
+        <v>39.99823479165183</v>
       </c>
       <c r="O24" t="n">
-        <v>6.324750483953956</v>
+        <v>6.324415766823987</v>
       </c>
       <c r="P24" t="n">
-        <v>384.1009253785767</v>
+        <v>384.0365230274504</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -28697,28 +28803,28 @@
         <v>0.0766</v>
       </c>
       <c r="I25" t="n">
-        <v>0.166466247706134</v>
+        <v>0.1713613925485472</v>
       </c>
       <c r="J25" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K25" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L25" t="n">
-        <v>0.04510341912967364</v>
+        <v>0.04785645350035284</v>
       </c>
       <c r="M25" t="n">
-        <v>4.100508413919146</v>
+        <v>4.104752454635754</v>
       </c>
       <c r="N25" t="n">
-        <v>26.75956475306477</v>
+        <v>26.7761435448672</v>
       </c>
       <c r="O25" t="n">
-        <v>5.172964793333198</v>
+        <v>5.174566991050285</v>
       </c>
       <c r="P25" t="n">
-        <v>378.0262467050542</v>
+        <v>377.9689383855999</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -28775,28 +28881,28 @@
         <v>0.0496</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1156752140731335</v>
+        <v>0.1172130862250488</v>
       </c>
       <c r="J26" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K26" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L26" t="n">
-        <v>0.01629881422594348</v>
+        <v>0.01686783756930776</v>
       </c>
       <c r="M26" t="n">
-        <v>4.559768017618133</v>
+        <v>4.54908827059004</v>
       </c>
       <c r="N26" t="n">
-        <v>36.8355875002302</v>
+        <v>36.69989662587344</v>
       </c>
       <c r="O26" t="n">
-        <v>6.069232859285447</v>
+        <v>6.058043960378089</v>
       </c>
       <c r="P26" t="n">
-        <v>383.4090758254684</v>
+        <v>383.3910716863879</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -28853,28 +28959,28 @@
         <v>0.0752</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1485308942564028</v>
+        <v>0.1540741667738597</v>
       </c>
       <c r="J27" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K27" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L27" t="n">
-        <v>0.0390286905856102</v>
+        <v>0.04196789588466954</v>
       </c>
       <c r="M27" t="n">
-        <v>3.76911588558261</v>
+        <v>3.782042898603456</v>
       </c>
       <c r="N27" t="n">
-        <v>24.77649244498052</v>
+        <v>24.83605812318918</v>
       </c>
       <c r="O27" t="n">
-        <v>4.977599064306055</v>
+        <v>4.983578846891977</v>
       </c>
       <c r="P27" t="n">
-        <v>367.4153954628533</v>
+        <v>367.3504993990023</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -28931,28 +29037,28 @@
         <v>0.0784</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1297422855334443</v>
+        <v>0.1365305893480934</v>
       </c>
       <c r="J28" t="n">
+        <v>249</v>
+      </c>
+      <c r="K28" t="n">
         <v>248</v>
       </c>
-      <c r="K28" t="n">
-        <v>247</v>
-      </c>
       <c r="L28" t="n">
-        <v>0.02223955231563968</v>
+        <v>0.02461043074128733</v>
       </c>
       <c r="M28" t="n">
-        <v>4.512552136638153</v>
+        <v>4.522912484637581</v>
       </c>
       <c r="N28" t="n">
-        <v>33.71543051624429</v>
+        <v>33.81797259691982</v>
       </c>
       <c r="O28" t="n">
-        <v>5.80649898960159</v>
+        <v>5.815322226404984</v>
       </c>
       <c r="P28" t="n">
-        <v>363.9347443927202</v>
+        <v>363.8551205055377</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -29009,28 +29115,28 @@
         <v>0.1741</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.01230559193445348</v>
+        <v>-0.006749579859764981</v>
       </c>
       <c r="J29" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K29" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L29" t="n">
-        <v>0.000266130503674411</v>
+        <v>8.028910214674667e-05</v>
       </c>
       <c r="M29" t="n">
-        <v>3.866674435794519</v>
+        <v>3.872448386685126</v>
       </c>
       <c r="N29" t="n">
-        <v>25.98959501651427</v>
+        <v>26.0448790633789</v>
       </c>
       <c r="O29" t="n">
-        <v>5.097999118920507</v>
+        <v>5.103418370404184</v>
       </c>
       <c r="P29" t="n">
-        <v>372.1781165372801</v>
+        <v>372.1129749486188</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -29068,7 +29174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD249"/>
+  <dimension ref="A1:AD250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66371,12 +66477,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>-35.63188640811581,174.51485466600744</t>
+          <t>-35.63192505352208,174.5149504960693</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>-35.63257189476763,174.5145334402675</t>
+          <t>-35.63262650950644,174.51466887061596</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -66510,6 +66616,158 @@
         </is>
       </c>
       <c r="AD249" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>-35.63192465429308,174.51494950608887</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>-35.63263245803209,174.51468362144698</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>-35.63331274986068,174.51434952819358</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>-35.63398154324153,174.51393261035318</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>-35.63453587093185,174.51330982549712</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>-35.63503305954513,174.51263930927607</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>-35.635540329361355,174.51199174542475</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>-35.63603105109763,174.5113225479886</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>-35.63656578598308,174.51071103489085</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>-35.63712206364779,174.5101282588811</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>-35.637678111251695,174.5095451600906</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>-35.638259831783024,174.509002997323</t>
+        </is>
+      </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>-35.638819831139145,174.50848027896552</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>-35.63941589129762,174.50799980607772</t>
+        </is>
+      </c>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>-35.640041639504325,174.50753421254126</t>
+        </is>
+      </c>
+      <c r="Q250" t="inlineStr">
+        <is>
+          <t>-35.64069253280686,174.50712319914004</t>
+        </is>
+      </c>
+      <c r="R250" t="inlineStr">
+        <is>
+          <t>-35.64132791642948,174.50667432690307</t>
+        </is>
+      </c>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>-35.641993099709985,174.5062902651347</t>
+        </is>
+      </c>
+      <c r="T250" t="inlineStr">
+        <is>
+          <t>-35.642639158494724,174.50586971881407</t>
+        </is>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>-35.643284131846826,174.50547670941822</t>
+        </is>
+      </c>
+      <c r="V250" t="inlineStr">
+        <is>
+          <t>-35.64392340106238,174.50508668097757</t>
+        </is>
+      </c>
+      <c r="W250" t="inlineStr">
+        <is>
+          <t>-35.64458208489589,174.5047092342666</t>
+        </is>
+      </c>
+      <c r="X250" t="inlineStr">
+        <is>
+          <t>-35.64523127059546,174.50434386331713</t>
+        </is>
+      </c>
+      <c r="Y250" t="inlineStr">
+        <is>
+          <t>-35.645880761329096,174.5039716277273</t>
+        </is>
+      </c>
+      <c r="Z250" t="inlineStr">
+        <is>
+          <t>-35.64657320769344,174.50369301557893</t>
+        </is>
+      </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>-35.64723757370175,174.50330047436256</t>
+        </is>
+      </c>
+      <c r="AB250" t="inlineStr">
+        <is>
+          <t>-35.64791714315195,174.50299384862578</t>
+        </is>
+      </c>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>-35.64862748854058,174.50285260028946</t>
+        </is>
+      </c>
+      <c r="AD250" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0094/nzd0094.xlsx
+++ b/data/nzd0094/nzd0094.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD250"/>
+  <dimension ref="A1:AD252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24285,6 +24285,198 @@
         </is>
       </c>
     </row>
+    <row r="251">
+      <c r="A251" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:11:50+00:00</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>367.7</v>
+      </c>
+      <c r="C251" t="n">
+        <v>395.63</v>
+      </c>
+      <c r="D251" t="n">
+        <v>399.76</v>
+      </c>
+      <c r="E251" t="n">
+        <v>384.38</v>
+      </c>
+      <c r="F251" t="n">
+        <v>382.25</v>
+      </c>
+      <c r="G251" t="n">
+        <v>377.94</v>
+      </c>
+      <c r="H251" t="n">
+        <v>375.71</v>
+      </c>
+      <c r="I251" t="n">
+        <v>368.9</v>
+      </c>
+      <c r="J251" t="n">
+        <v>368.58</v>
+      </c>
+      <c r="K251" t="n">
+        <v>371.64</v>
+      </c>
+      <c r="L251" t="n">
+        <v>373.18</v>
+      </c>
+      <c r="M251" t="n">
+        <v>382.28</v>
+      </c>
+      <c r="N251" t="n">
+        <v>386.15</v>
+      </c>
+      <c r="O251" t="n">
+        <v>380.31</v>
+      </c>
+      <c r="P251" t="n">
+        <v>375.54</v>
+      </c>
+      <c r="Q251" t="n">
+        <v>378.52</v>
+      </c>
+      <c r="R251" t="n">
+        <v>376</v>
+      </c>
+      <c r="S251" t="n">
+        <v>386.37</v>
+      </c>
+      <c r="T251" t="n">
+        <v>390.24</v>
+      </c>
+      <c r="U251" t="n">
+        <v>398.18</v>
+      </c>
+      <c r="V251" t="n">
+        <v>399.92</v>
+      </c>
+      <c r="W251" t="n">
+        <v>398.87</v>
+      </c>
+      <c r="X251" t="n">
+        <v>399.59</v>
+      </c>
+      <c r="Y251" t="n">
+        <v>392.17</v>
+      </c>
+      <c r="Z251" t="n">
+        <v>395.64</v>
+      </c>
+      <c r="AA251" t="n">
+        <v>381.84</v>
+      </c>
+      <c r="AB251" t="n">
+        <v>379.4</v>
+      </c>
+      <c r="AC251" t="n">
+        <v>380.67</v>
+      </c>
+      <c r="AD251" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:11:44+00:00</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>371.97</v>
+      </c>
+      <c r="C252" t="n">
+        <v>400.13</v>
+      </c>
+      <c r="D252" t="n">
+        <v>399.76</v>
+      </c>
+      <c r="E252" t="n">
+        <v>384.42</v>
+      </c>
+      <c r="F252" t="n">
+        <v>382.02</v>
+      </c>
+      <c r="G252" t="n">
+        <v>376.36</v>
+      </c>
+      <c r="H252" t="n">
+        <v>374.97</v>
+      </c>
+      <c r="I252" t="n">
+        <v>368.57</v>
+      </c>
+      <c r="J252" t="n">
+        <v>368.74</v>
+      </c>
+      <c r="K252" t="n">
+        <v>371.25</v>
+      </c>
+      <c r="L252" t="n">
+        <v>372.63</v>
+      </c>
+      <c r="M252" t="n">
+        <v>382.23</v>
+      </c>
+      <c r="N252" t="n">
+        <v>385.59</v>
+      </c>
+      <c r="O252" t="n">
+        <v>380.31</v>
+      </c>
+      <c r="P252" t="n">
+        <v>375.5</v>
+      </c>
+      <c r="Q252" t="n">
+        <v>378.85</v>
+      </c>
+      <c r="R252" t="n">
+        <v>375.53</v>
+      </c>
+      <c r="S252" t="n">
+        <v>386.42</v>
+      </c>
+      <c r="T252" t="n">
+        <v>389.89</v>
+      </c>
+      <c r="U252" t="n">
+        <v>397.7</v>
+      </c>
+      <c r="V252" t="n">
+        <v>398.75</v>
+      </c>
+      <c r="W252" t="n">
+        <v>398.51</v>
+      </c>
+      <c r="X252" t="n">
+        <v>398.36</v>
+      </c>
+      <c r="Y252" t="n">
+        <v>391.78</v>
+      </c>
+      <c r="Z252" t="n">
+        <v>394.82</v>
+      </c>
+      <c r="AA252" t="n">
+        <v>381.48</v>
+      </c>
+      <c r="AB252" t="n">
+        <v>378.06</v>
+      </c>
+      <c r="AC252" t="n">
+        <v>379.76</v>
+      </c>
+      <c r="AD252" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24296,7 +24488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B253"/>
+  <dimension ref="A1:B255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26829,6 +27021,26 @@
       </c>
       <c r="B253" t="n">
         <v>0.73</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>0.88</v>
       </c>
     </row>
   </sheetData>
@@ -26997,28 +27209,28 @@
         <v>0.0102</v>
       </c>
       <c r="I2" t="n">
-        <v>1.04812396942221</v>
+        <v>0.9992245206269277</v>
       </c>
       <c r="J2" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K2" t="n">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04067112637585502</v>
+        <v>0.03756463208055971</v>
       </c>
       <c r="M2" t="n">
-        <v>26.75447718800512</v>
+        <v>26.70603605140351</v>
       </c>
       <c r="N2" t="n">
-        <v>1113.134207488573</v>
+        <v>1109.230349004731</v>
       </c>
       <c r="O2" t="n">
-        <v>33.36366597795531</v>
+        <v>33.30510995334997</v>
       </c>
       <c r="P2" t="n">
-        <v>368.1400370200131</v>
+        <v>368.7458444119159</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -27079,28 +27291,28 @@
         <v>0.0104</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8958762362542226</v>
+        <v>0.8792727047347979</v>
       </c>
       <c r="J3" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K3" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04574971643703163</v>
+        <v>0.04484857380218832</v>
       </c>
       <c r="M3" t="n">
-        <v>22.39742786989591</v>
+        <v>22.25686400833488</v>
       </c>
       <c r="N3" t="n">
-        <v>768.9646605899472</v>
+        <v>762.8336820261594</v>
       </c>
       <c r="O3" t="n">
-        <v>27.73021205454346</v>
+        <v>27.61944391232668</v>
       </c>
       <c r="P3" t="n">
-        <v>383.301347976467</v>
+        <v>383.5016127277983</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -27161,28 +27373,28 @@
         <v>0.0106</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3325009780912476</v>
+        <v>0.3498940143617489</v>
       </c>
       <c r="J4" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K4" t="n">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006970085829648198</v>
+        <v>0.007844146848278277</v>
       </c>
       <c r="M4" t="n">
-        <v>21.41122991253868</v>
+        <v>21.33052499221344</v>
       </c>
       <c r="N4" t="n">
-        <v>685.9349556779833</v>
+        <v>680.7746694638166</v>
       </c>
       <c r="O4" t="n">
-        <v>26.19035997610539</v>
+        <v>26.09165900175412</v>
       </c>
       <c r="P4" t="n">
-        <v>381.6465560410489</v>
+        <v>381.4332742739264</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -27243,28 +27455,28 @@
         <v>0.0239</v>
       </c>
       <c r="I5" t="n">
-        <v>0.783365744425969</v>
+        <v>0.8000278063574083</v>
       </c>
       <c r="J5" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K5" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0750959106647977</v>
+        <v>0.07919471812488699</v>
       </c>
       <c r="M5" t="n">
-        <v>15.23899129610336</v>
+        <v>15.19658561872947</v>
       </c>
       <c r="N5" t="n">
-        <v>346.6779701721783</v>
+        <v>344.5950728747879</v>
       </c>
       <c r="O5" t="n">
-        <v>18.61929027036687</v>
+        <v>18.56327214891782</v>
       </c>
       <c r="P5" t="n">
-        <v>354.1301013749131</v>
+        <v>353.9332743314175</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27321,28 +27533,28 @@
         <v>0.0308</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2905757109288102</v>
+        <v>0.322991597566656</v>
       </c>
       <c r="J6" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K6" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01846278846981286</v>
+        <v>0.02281517378479492</v>
       </c>
       <c r="M6" t="n">
-        <v>11.63867780570443</v>
+        <v>11.69988593578091</v>
       </c>
       <c r="N6" t="n">
-        <v>200.8758074227886</v>
+        <v>201.902400059848</v>
       </c>
       <c r="O6" t="n">
-        <v>14.17306626749443</v>
+        <v>14.20923643479297</v>
       </c>
       <c r="P6" t="n">
-        <v>356.1076993075171</v>
+        <v>355.720273446511</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27399,28 +27611,28 @@
         <v>0.0359</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2184283610396531</v>
+        <v>0.2496121263469235</v>
       </c>
       <c r="J7" t="n">
+        <v>251</v>
+      </c>
+      <c r="K7" t="n">
         <v>249</v>
       </c>
-      <c r="K7" t="n">
-        <v>247</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.01441938910736063</v>
+        <v>0.01876388208373025</v>
       </c>
       <c r="M7" t="n">
-        <v>10.23822761456857</v>
+        <v>10.26717680031411</v>
       </c>
       <c r="N7" t="n">
-        <v>147.1210468413169</v>
+        <v>148.4204447019976</v>
       </c>
       <c r="O7" t="n">
-        <v>12.12934651336653</v>
+        <v>12.18279297624308</v>
       </c>
       <c r="P7" t="n">
-        <v>353.5903514236348</v>
+        <v>353.2196044399316</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27477,28 +27689,28 @@
         <v>0.0369</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1287850402835656</v>
+        <v>0.1606872553367213</v>
       </c>
       <c r="J8" t="n">
+        <v>251</v>
+      </c>
+      <c r="K8" t="n">
         <v>249</v>
       </c>
-      <c r="K8" t="n">
-        <v>247</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.007248249117714045</v>
+        <v>0.01115627307823586</v>
       </c>
       <c r="M8" t="n">
-        <v>8.238937664912342</v>
+        <v>8.297720471397213</v>
       </c>
       <c r="N8" t="n">
-        <v>102.4825325667332</v>
+        <v>104.2516483111329</v>
       </c>
       <c r="O8" t="n">
-        <v>10.12336567386228</v>
+        <v>10.21036964615547</v>
       </c>
       <c r="P8" t="n">
-        <v>353.7462163795142</v>
+        <v>353.3669198978601</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27555,28 +27767,28 @@
         <v>0.0422</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1954829348066763</v>
+        <v>0.2138069250118314</v>
       </c>
       <c r="J9" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K9" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02433722052410514</v>
+        <v>0.02912369364073075</v>
       </c>
       <c r="M9" t="n">
-        <v>6.73367902858859</v>
+        <v>6.75891465042635</v>
       </c>
       <c r="N9" t="n">
-        <v>69.66439733626605</v>
+        <v>69.97122172777307</v>
       </c>
       <c r="O9" t="n">
-        <v>8.346520073435759</v>
+        <v>8.364880257826353</v>
       </c>
       <c r="P9" t="n">
-        <v>353.0457897741736</v>
+        <v>352.829058662966</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27633,28 +27845,28 @@
         <v>0.045</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2726371528491806</v>
+        <v>0.28573624934641</v>
       </c>
       <c r="J10" t="n">
+        <v>251</v>
+      </c>
+      <c r="K10" t="n">
         <v>249</v>
       </c>
-      <c r="K10" t="n">
-        <v>247</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.04978906397703975</v>
+        <v>0.05497862473408111</v>
       </c>
       <c r="M10" t="n">
-        <v>6.518898357859396</v>
+        <v>6.529817508082123</v>
       </c>
       <c r="N10" t="n">
-        <v>64.6051353907951</v>
+        <v>64.52911882537245</v>
       </c>
       <c r="O10" t="n">
-        <v>8.037731980527536</v>
+        <v>8.033001856427799</v>
       </c>
       <c r="P10" t="n">
-        <v>353.9366680758432</v>
+        <v>353.7816641561284</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27711,28 +27923,28 @@
         <v>0.0478</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3328883254157755</v>
+        <v>0.3442978762367262</v>
       </c>
       <c r="J11" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K11" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L11" t="n">
-        <v>0.08054006330557106</v>
+        <v>0.08660584437208874</v>
       </c>
       <c r="M11" t="n">
-        <v>6.201861026481155</v>
+        <v>6.209530252666155</v>
       </c>
       <c r="N11" t="n">
-        <v>57.5284133494354</v>
+        <v>57.40347570923051</v>
       </c>
       <c r="O11" t="n">
-        <v>7.584748733441036</v>
+        <v>7.576508147506376</v>
       </c>
       <c r="P11" t="n">
-        <v>356.1005799506773</v>
+        <v>355.9656326463019</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27789,28 +28001,28 @@
         <v>0.0536</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2429118978436709</v>
+        <v>0.2475701711083604</v>
       </c>
       <c r="J12" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K12" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05779854671811635</v>
+        <v>0.06083211515054088</v>
       </c>
       <c r="M12" t="n">
-        <v>5.244855236948338</v>
+        <v>5.224192377188697</v>
       </c>
       <c r="N12" t="n">
-        <v>43.74101420031785</v>
+        <v>43.4475631440711</v>
       </c>
       <c r="O12" t="n">
-        <v>6.613698980171221</v>
+        <v>6.591476552645173</v>
       </c>
       <c r="P12" t="n">
-        <v>363.8107937141089</v>
+        <v>363.7557010943711</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -27867,28 +28079,28 @@
         <v>0.0468</v>
       </c>
       <c r="I13" t="n">
-        <v>0.23392286897527</v>
+        <v>0.2407396573844189</v>
       </c>
       <c r="J13" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K13" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05644544046810995</v>
+        <v>0.06041876693970671</v>
       </c>
       <c r="M13" t="n">
-        <v>5.320556754989881</v>
+        <v>5.312186179108162</v>
       </c>
       <c r="N13" t="n">
-        <v>41.59565218522744</v>
+        <v>41.38245253577153</v>
       </c>
       <c r="O13" t="n">
-        <v>6.449469139799604</v>
+        <v>6.432919441106932</v>
       </c>
       <c r="P13" t="n">
-        <v>372.161351508127</v>
+        <v>372.0807238786096</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -27945,28 +28157,28 @@
         <v>0.0508</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1334970273525931</v>
+        <v>0.1339284873380789</v>
       </c>
       <c r="J14" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K14" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02385318618060039</v>
+        <v>0.0244210342144896</v>
       </c>
       <c r="M14" t="n">
-        <v>4.736719031951032</v>
+        <v>4.701264314491189</v>
       </c>
       <c r="N14" t="n">
-        <v>33.16472165321639</v>
+        <v>32.90052110571119</v>
       </c>
       <c r="O14" t="n">
-        <v>5.758881979448475</v>
+        <v>5.735897585008922</v>
       </c>
       <c r="P14" t="n">
-        <v>382.0962407033642</v>
+        <v>382.0911423890702</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -28023,28 +28235,28 @@
         <v>0.0555</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1240776838801887</v>
+        <v>0.1245069555579758</v>
       </c>
       <c r="J15" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K15" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02022491948005833</v>
+        <v>0.02071783577265462</v>
       </c>
       <c r="M15" t="n">
-        <v>4.757526411495925</v>
+        <v>4.721513151399819</v>
       </c>
       <c r="N15" t="n">
-        <v>33.91496455999522</v>
+        <v>33.64411894588145</v>
       </c>
       <c r="O15" t="n">
-        <v>5.823655601080409</v>
+        <v>5.800355070672954</v>
       </c>
       <c r="P15" t="n">
-        <v>376.785674670744</v>
+        <v>376.7805973035142</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -28101,28 +28313,28 @@
         <v>0.0487</v>
       </c>
       <c r="I16" t="n">
-        <v>0.01897985211326518</v>
+        <v>0.01493489626751607</v>
       </c>
       <c r="J16" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K16" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0003857554474476776</v>
+        <v>0.0002428955396633903</v>
       </c>
       <c r="M16" t="n">
-        <v>5.393241246098358</v>
+        <v>5.366518408046066</v>
       </c>
       <c r="N16" t="n">
-        <v>42.5118114103389</v>
+        <v>42.21124195008922</v>
       </c>
       <c r="O16" t="n">
-        <v>6.520108236090786</v>
+        <v>6.497017927487135</v>
       </c>
       <c r="P16" t="n">
-        <v>377.3361083194411</v>
+        <v>377.3840284788789</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -28179,28 +28391,28 @@
         <v>0.0534</v>
       </c>
       <c r="I17" t="n">
-        <v>0.035980310505958</v>
+        <v>0.04020146575433275</v>
       </c>
       <c r="J17" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K17" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L17" t="n">
-        <v>0.001309854773239083</v>
+        <v>0.001662017744166078</v>
       </c>
       <c r="M17" t="n">
-        <v>5.278456262295775</v>
+        <v>5.256976909457275</v>
       </c>
       <c r="N17" t="n">
-        <v>44.95117255240465</v>
+        <v>44.63488951224173</v>
       </c>
       <c r="O17" t="n">
-        <v>6.704563561664894</v>
+        <v>6.68093477832569</v>
       </c>
       <c r="P17" t="n">
-        <v>375.31743371159</v>
+        <v>375.2674235778754</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -28257,28 +28469,28 @@
         <v>0.0579</v>
       </c>
       <c r="I18" t="n">
-        <v>0.06501720557101413</v>
+        <v>0.06192184478542932</v>
       </c>
       <c r="J18" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K18" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L18" t="n">
-        <v>0.004821374100300257</v>
+        <v>0.004450100684913472</v>
       </c>
       <c r="M18" t="n">
-        <v>5.19957147654061</v>
+        <v>5.169826897445415</v>
       </c>
       <c r="N18" t="n">
-        <v>39.67813327421314</v>
+        <v>39.38577919970044</v>
       </c>
       <c r="O18" t="n">
-        <v>6.299058125959241</v>
+        <v>6.27580904742173</v>
       </c>
       <c r="P18" t="n">
-        <v>375.8259095463685</v>
+        <v>375.8625252026371</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -28335,28 +28547,28 @@
         <v>0.053</v>
       </c>
       <c r="I19" t="n">
-        <v>0.09381129846239596</v>
+        <v>0.1011585055120086</v>
       </c>
       <c r="J19" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K19" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="L19" t="n">
-        <v>0.009039149286562354</v>
+        <v>0.01064615815596182</v>
       </c>
       <c r="M19" t="n">
-        <v>5.420667727077299</v>
+        <v>5.413862667657759</v>
       </c>
       <c r="N19" t="n">
-        <v>44.21802875737234</v>
+        <v>44.00602511964394</v>
       </c>
       <c r="O19" t="n">
-        <v>6.649663807845652</v>
+        <v>6.633703725645572</v>
       </c>
       <c r="P19" t="n">
-        <v>379.6665252509939</v>
+        <v>379.5800719600987</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -28413,28 +28625,28 @@
         <v>0.049</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0690334242343717</v>
+        <v>0.0750741076747956</v>
       </c>
       <c r="J20" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K20" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L20" t="n">
-        <v>0.004982821020412143</v>
+        <v>0.005979681807700032</v>
       </c>
       <c r="M20" t="n">
-        <v>5.150882649848843</v>
+        <v>5.139366246694038</v>
       </c>
       <c r="N20" t="n">
-        <v>42.5866683356174</v>
+        <v>42.33539767247147</v>
       </c>
       <c r="O20" t="n">
-        <v>6.525846177747174</v>
+        <v>6.506565735660516</v>
       </c>
       <c r="P20" t="n">
-        <v>384.8214481310692</v>
+        <v>384.7492542611178</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -28491,28 +28703,28 @@
         <v>0.0506</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1951386989316932</v>
+        <v>0.2029370012484338</v>
       </c>
       <c r="J21" t="n">
+        <v>251</v>
+      </c>
+      <c r="K21" t="n">
         <v>249</v>
       </c>
-      <c r="K21" t="n">
-        <v>247</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.03983450921865872</v>
+        <v>0.04351991914863385</v>
       </c>
       <c r="M21" t="n">
-        <v>4.943743447776376</v>
+        <v>4.945494032367912</v>
       </c>
       <c r="N21" t="n">
-        <v>41.40806104075629</v>
+        <v>41.23080989231283</v>
       </c>
       <c r="O21" t="n">
-        <v>6.434909559640779</v>
+        <v>6.421122167683219</v>
       </c>
       <c r="P21" t="n">
-        <v>388.3380638559054</v>
+        <v>388.2453498989753</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -28569,28 +28781,28 @@
         <v>0.057</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1360517717798947</v>
+        <v>0.1502082546983211</v>
       </c>
       <c r="J22" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K22" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="L22" t="n">
-        <v>0.02529932051921135</v>
+        <v>0.03071635896115521</v>
       </c>
       <c r="M22" t="n">
-        <v>4.367042206729914</v>
+        <v>4.407140786260808</v>
       </c>
       <c r="N22" t="n">
-        <v>32.68368081157595</v>
+        <v>32.94711190810649</v>
       </c>
       <c r="O22" t="n">
-        <v>5.71696430035871</v>
+        <v>5.739957483127073</v>
       </c>
       <c r="P22" t="n">
-        <v>387.5504747459482</v>
+        <v>387.3839087492571</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -28647,28 +28859,28 @@
         <v>0.0611</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1737248967232835</v>
+        <v>0.1885111349704542</v>
       </c>
       <c r="J23" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K23" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="L23" t="n">
-        <v>0.03976888595703776</v>
+        <v>0.04652623541313172</v>
       </c>
       <c r="M23" t="n">
-        <v>4.396120064846692</v>
+        <v>4.436277830013648</v>
       </c>
       <c r="N23" t="n">
-        <v>33.3977045401545</v>
+        <v>33.70027559835815</v>
       </c>
       <c r="O23" t="n">
-        <v>5.77907471314868</v>
+        <v>5.805193846751213</v>
       </c>
       <c r="P23" t="n">
-        <v>385.5447858186903</v>
+        <v>385.3708026998889</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -28725,28 +28937,28 @@
         <v>0.064</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2296974602044319</v>
+        <v>0.2450287548506633</v>
       </c>
       <c r="J24" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K24" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L24" t="n">
-        <v>0.05709166599021309</v>
+        <v>0.06459239102959968</v>
       </c>
       <c r="M24" t="n">
-        <v>4.99185328073851</v>
+        <v>5.017257150323927</v>
       </c>
       <c r="N24" t="n">
-        <v>39.99823479165183</v>
+        <v>40.29454687256938</v>
       </c>
       <c r="O24" t="n">
-        <v>6.324415766823987</v>
+        <v>6.347798584751203</v>
       </c>
       <c r="P24" t="n">
-        <v>384.0365230274504</v>
+        <v>383.8560608630766</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -28803,28 +29015,28 @@
         <v>0.0766</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1713613925485472</v>
+        <v>0.18774774044718</v>
       </c>
       <c r="J25" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K25" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="L25" t="n">
-        <v>0.04785645350035284</v>
+        <v>0.05645664509766957</v>
       </c>
       <c r="M25" t="n">
-        <v>4.104752454635754</v>
+        <v>4.141976093418699</v>
       </c>
       <c r="N25" t="n">
-        <v>26.7761435448672</v>
+        <v>27.26119150613868</v>
       </c>
       <c r="O25" t="n">
-        <v>5.174566991050285</v>
+        <v>5.221225096290973</v>
       </c>
       <c r="P25" t="n">
-        <v>377.9689383855999</v>
+        <v>377.7761273532345</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -28881,28 +29093,28 @@
         <v>0.0496</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1172130862250488</v>
+        <v>0.1323250803001057</v>
       </c>
       <c r="J26" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K26" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="L26" t="n">
-        <v>0.01686783756930776</v>
+        <v>0.02142856094171797</v>
       </c>
       <c r="M26" t="n">
-        <v>4.54908827059004</v>
+        <v>4.586312212608749</v>
       </c>
       <c r="N26" t="n">
-        <v>36.69989662587344</v>
+        <v>37.00261902708647</v>
       </c>
       <c r="O26" t="n">
-        <v>6.058043960378089</v>
+        <v>6.082977809189054</v>
       </c>
       <c r="P26" t="n">
-        <v>383.3910716863879</v>
+        <v>383.213259405981</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -28959,28 +29171,28 @@
         <v>0.0752</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1540741667738597</v>
+        <v>0.1717728673883384</v>
       </c>
       <c r="J27" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K27" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="L27" t="n">
-        <v>0.04196789588466954</v>
+        <v>0.05091291314239577</v>
       </c>
       <c r="M27" t="n">
-        <v>3.782042898603456</v>
+        <v>3.842490427528412</v>
       </c>
       <c r="N27" t="n">
-        <v>24.83605812318918</v>
+        <v>25.45281671483618</v>
       </c>
       <c r="O27" t="n">
-        <v>4.983578846891977</v>
+        <v>5.045078464685775</v>
       </c>
       <c r="P27" t="n">
-        <v>367.3504993990023</v>
+        <v>367.1422460127793</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -29037,28 +29249,28 @@
         <v>0.0784</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1365305893480934</v>
+        <v>0.1560396964930587</v>
       </c>
       <c r="J28" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K28" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L28" t="n">
-        <v>0.02461043074128733</v>
+        <v>0.03155115944820375</v>
       </c>
       <c r="M28" t="n">
-        <v>4.522912484637581</v>
+        <v>4.570866565676692</v>
       </c>
       <c r="N28" t="n">
-        <v>33.81797259691982</v>
+        <v>34.54042358024453</v>
       </c>
       <c r="O28" t="n">
-        <v>5.815322226404984</v>
+        <v>5.877110138515742</v>
       </c>
       <c r="P28" t="n">
-        <v>363.8551205055377</v>
+        <v>363.6251303309132</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -29115,28 +29327,28 @@
         <v>0.1741</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.006749579859764981</v>
+        <v>0.007584734782068776</v>
       </c>
       <c r="J29" t="n">
+        <v>251</v>
+      </c>
+      <c r="K29" t="n">
         <v>249</v>
       </c>
-      <c r="K29" t="n">
-        <v>247</v>
-      </c>
       <c r="L29" t="n">
-        <v>8.028910214674667e-05</v>
+        <v>0.0001010794667971604</v>
       </c>
       <c r="M29" t="n">
-        <v>3.872448386685126</v>
+        <v>3.896575430807054</v>
       </c>
       <c r="N29" t="n">
-        <v>26.0448790633789</v>
+        <v>26.37387863235298</v>
       </c>
       <c r="O29" t="n">
-        <v>5.103418370404184</v>
+        <v>5.135550470237146</v>
       </c>
       <c r="P29" t="n">
-        <v>372.1129749486188</v>
+        <v>371.9440563462746</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -29174,7 +29386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD250"/>
+  <dimension ref="A1:AD252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66773,6 +66985,310 @@
         </is>
       </c>
     </row>
+    <row r="251">
+      <c r="A251" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:11:50+00:00</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>-35.63195024485504,174.51501296385442</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>-35.63271290267551,174.51488310437125</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>-35.63338053920866,174.51451762971445</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>-35.633989226877695,174.51394743118394</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>-35.63456187584889,174.51334665699858</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>-35.63506859295978,174.5126858369454</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>-35.63558263710502,174.5120471433331</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>-35.636068278978605,174.51137167010134</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>-35.636597687058696,174.51075355751965</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>-35.637149109986495,174.51016439916413</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>-35.63769132989954,174.50956282331128</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>-35.63827626539903,174.50902602702513</t>
+        </is>
+      </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>-35.638829547207926,174.50849809116892</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>-35.63942776489463,174.5080274658451</t>
+        </is>
+      </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>-35.64005028252711,174.50755434663301</t>
+        </is>
+      </c>
+      <c r="Q251" t="inlineStr">
+        <is>
+          <t>-35.64070707127435,174.50715600112758</t>
+        </is>
+      </c>
+      <c r="R251" t="inlineStr">
+        <is>
+          <t>-35.64133187305522,174.5066827496955</t>
+        </is>
+      </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>-35.642005251152455,174.50631546042064</t>
+        </is>
+      </c>
+      <c r="T251" t="inlineStr">
+        <is>
+          <t>-35.64264754990371,174.50588711793927</t>
+        </is>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>-35.64329656249096,174.50550513353855</t>
+        </is>
+      </c>
+      <c r="V251" t="inlineStr">
+        <is>
+          <t>-35.64394096800718,174.50513257485218</t>
+        </is>
+      </c>
+      <c r="W251" t="inlineStr">
+        <is>
+          <t>-35.64459474013025,174.50474331057512</t>
+        </is>
+      </c>
+      <c r="X251" t="inlineStr">
+        <is>
+          <t>-35.64524217182347,174.5043778906054</t>
+        </is>
+      </c>
+      <c r="Y251" t="inlineStr">
+        <is>
+          <t>-35.645892422219305,174.5040155241669</t>
+        </is>
+      </c>
+      <c r="Z251" t="inlineStr">
+        <is>
+          <t>-35.64659352923169,174.5037712027713</t>
+        </is>
+      </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>-35.647249033734795,174.50334456679334</t>
+        </is>
+      </c>
+      <c r="AB251" t="inlineStr">
+        <is>
+          <t>-35.64792669574566,174.5030399869395</t>
+        </is>
+      </c>
+      <c r="AC251" t="inlineStr">
+        <is>
+          <t>-35.64863167218504,174.50287950568932</t>
+        </is>
+      </c>
+      <c r="AD251" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:11:44+00:00</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>-35.63196729190289,174.5150552360541</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>-35.63273086793386,174.51492765396105</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>-35.63338053920866,174.51451762971445</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>-35.6339894201767,174.51394780403507</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>-35.63456051958368,174.51334473608068</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>-35.635058862841205,174.51267309626235</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>-35.63557807994034,174.51204117616112</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>-35.636066255058104,174.5113689995405</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>-35.63659866299957,174.51075485840366</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>-35.637146734295044,174.51016122467885</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>-35.63768797955128,174.50955834645757</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>-35.63827596876341,174.50902561132645</t>
+        </is>
+      </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>-35.63882674256978,174.50849294950152</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>-35.63942776489463,174.5080274658451</t>
+        </is>
+      </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>-35.64005011470146,174.50755395567975</t>
+        </is>
+      </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>-35.64070849071004,174.50715920368913</t>
+        </is>
+      </c>
+      <c r="R252" t="inlineStr">
+        <is>
+          <t>-35.64132975985747,174.50667825115855</t>
+        </is>
+      </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>-35.6420054804249,174.50631593580349</t>
+        </is>
+      </c>
+      <c r="T252" t="inlineStr">
+        <is>
+          <t>-35.64264594498963,174.50588379023748</t>
+        </is>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>-35.64329451909789,174.50550046107983</t>
+        </is>
+      </c>
+      <c r="V252" t="inlineStr">
+        <is>
+          <t>-35.643936490160215,174.5051208764117</t>
+        </is>
+      </c>
+      <c r="W252" t="inlineStr">
+        <is>
+          <t>-35.644593396212024,174.5047396918516</t>
+        </is>
+      </c>
+      <c r="X252" t="inlineStr">
+        <is>
+          <t>-35.64523812091512,174.50436524602293</t>
+        </is>
+      </c>
+      <c r="Y252" t="inlineStr">
+        <is>
+          <t>-35.64589133424221,174.50401142856555</t>
+        </is>
+      </c>
+      <c r="Z252" t="inlineStr">
+        <is>
+          <t>-35.646591286480344,174.50376257376573</t>
+        </is>
+      </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>-35.64724804910253,174.50334077842172</t>
+        </is>
+      </c>
+      <c r="AB252" t="inlineStr">
+        <is>
+          <t>-35.64792372579964,174.50302564231185</t>
+        </is>
+      </c>
+      <c r="AC252" t="inlineStr">
+        <is>
+          <t>-35.648630137058134,174.50286963314312</t>
+        </is>
+      </c>
+      <c r="AD252" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0094/nzd0094.xlsx
+++ b/data/nzd0094/nzd0094.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD252"/>
+  <dimension ref="A1:AD254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24477,6 +24477,198 @@
         </is>
       </c>
     </row>
+    <row r="253">
+      <c r="A253" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>375.57</v>
+      </c>
+      <c r="C253" t="n">
+        <v>404.71</v>
+      </c>
+      <c r="D253" t="n">
+        <v>399.76</v>
+      </c>
+      <c r="E253" t="n">
+        <v>385.21</v>
+      </c>
+      <c r="F253" t="n">
+        <v>381.05</v>
+      </c>
+      <c r="G253" t="n">
+        <v>375.33</v>
+      </c>
+      <c r="H253" t="n">
+        <v>373.13</v>
+      </c>
+      <c r="I253" t="n">
+        <v>367.96</v>
+      </c>
+      <c r="J253" t="n">
+        <v>368.28</v>
+      </c>
+      <c r="K253" t="n">
+        <v>370.13</v>
+      </c>
+      <c r="L253" t="n">
+        <v>372.76</v>
+      </c>
+      <c r="M253" t="n">
+        <v>381.45</v>
+      </c>
+      <c r="N253" t="n">
+        <v>385.79</v>
+      </c>
+      <c r="O253" t="n">
+        <v>379.16</v>
+      </c>
+      <c r="P253" t="n">
+        <v>375.85</v>
+      </c>
+      <c r="Q253" t="n">
+        <v>377.87</v>
+      </c>
+      <c r="R253" t="n">
+        <v>375.82</v>
+      </c>
+      <c r="S253" t="n">
+        <v>385.2</v>
+      </c>
+      <c r="T253" t="n">
+        <v>389.05</v>
+      </c>
+      <c r="U253" t="n">
+        <v>397.16</v>
+      </c>
+      <c r="V253" t="n">
+        <v>398.38</v>
+      </c>
+      <c r="W253" t="n">
+        <v>396.08</v>
+      </c>
+      <c r="X253" t="n">
+        <v>397.53</v>
+      </c>
+      <c r="Y253" t="n">
+        <v>390.4</v>
+      </c>
+      <c r="Z253" t="n">
+        <v>394.67</v>
+      </c>
+      <c r="AA253" t="n">
+        <v>380.77</v>
+      </c>
+      <c r="AB253" t="n">
+        <v>377.57</v>
+      </c>
+      <c r="AC253" t="n">
+        <v>378.83</v>
+      </c>
+      <c r="AD253" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>375.57</v>
+      </c>
+      <c r="C254" t="n">
+        <v>404.71</v>
+      </c>
+      <c r="D254" t="n">
+        <v>389.8</v>
+      </c>
+      <c r="E254" t="n">
+        <v>382.57</v>
+      </c>
+      <c r="F254" t="n">
+        <v>377.29</v>
+      </c>
+      <c r="G254" t="n">
+        <v>370.96</v>
+      </c>
+      <c r="H254" t="n">
+        <v>368.84</v>
+      </c>
+      <c r="I254" t="n">
+        <v>364.95</v>
+      </c>
+      <c r="J254" t="n">
+        <v>365.78</v>
+      </c>
+      <c r="K254" t="n">
+        <v>367.67</v>
+      </c>
+      <c r="L254" t="n">
+        <v>369.96</v>
+      </c>
+      <c r="M254" t="n">
+        <v>378.2</v>
+      </c>
+      <c r="N254" t="n">
+        <v>382.44</v>
+      </c>
+      <c r="O254" t="n">
+        <v>377.21</v>
+      </c>
+      <c r="P254" t="n">
+        <v>374.5</v>
+      </c>
+      <c r="Q254" t="n">
+        <v>375.17</v>
+      </c>
+      <c r="R254" t="n">
+        <v>373.37</v>
+      </c>
+      <c r="S254" t="n">
+        <v>383.1</v>
+      </c>
+      <c r="T254" t="n">
+        <v>386.57</v>
+      </c>
+      <c r="U254" t="n">
+        <v>393.64</v>
+      </c>
+      <c r="V254" t="n">
+        <v>394.64</v>
+      </c>
+      <c r="W254" t="n">
+        <v>392.98</v>
+      </c>
+      <c r="X254" t="n">
+        <v>394.31</v>
+      </c>
+      <c r="Y254" t="n">
+        <v>388.08</v>
+      </c>
+      <c r="Z254" t="n">
+        <v>392.64</v>
+      </c>
+      <c r="AA254" t="n">
+        <v>377.6</v>
+      </c>
+      <c r="AB254" t="n">
+        <v>375.52</v>
+      </c>
+      <c r="AC254" t="n">
+        <v>378.19</v>
+      </c>
+      <c r="AD254" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24488,7 +24680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B255"/>
+  <dimension ref="A1:B257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27041,6 +27233,26 @@
       </c>
       <c r="B255" t="n">
         <v>0.88</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>-0.63</v>
       </c>
     </row>
   </sheetData>
@@ -27209,28 +27421,28 @@
         <v>0.0102</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9992245206269277</v>
+        <v>0.9628084309279903</v>
       </c>
       <c r="J2" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K2" t="n">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03756463208055971</v>
+        <v>0.03547530437611879</v>
       </c>
       <c r="M2" t="n">
-        <v>26.70603605140351</v>
+        <v>26.62345235630442</v>
       </c>
       <c r="N2" t="n">
-        <v>1109.230349004731</v>
+        <v>1102.942060035547</v>
       </c>
       <c r="O2" t="n">
-        <v>33.30510995334997</v>
+        <v>33.21057151022166</v>
       </c>
       <c r="P2" t="n">
-        <v>368.7458444119159</v>
+        <v>369.1987644395404</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -27291,28 +27503,28 @@
         <v>0.0104</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8792727047347979</v>
+        <v>0.8754918685113454</v>
       </c>
       <c r="J3" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K3" t="n">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04484857380218832</v>
+        <v>0.04522085982224278</v>
       </c>
       <c r="M3" t="n">
-        <v>22.25686400833488</v>
+        <v>22.07243802779213</v>
       </c>
       <c r="N3" t="n">
-        <v>762.8336820261594</v>
+        <v>756.0911567557039</v>
       </c>
       <c r="O3" t="n">
-        <v>27.61944391232668</v>
+        <v>27.49711178934442</v>
       </c>
       <c r="P3" t="n">
-        <v>383.5016127277983</v>
+        <v>383.5474185371847</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -27373,28 +27585,28 @@
         <v>0.0106</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3498940143617489</v>
+        <v>0.357325545695202</v>
       </c>
       <c r="J4" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K4" t="n">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L4" t="n">
-        <v>0.007844146848278277</v>
+        <v>0.008319954348276148</v>
       </c>
       <c r="M4" t="n">
-        <v>21.33052499221344</v>
+        <v>21.20120079221915</v>
       </c>
       <c r="N4" t="n">
-        <v>680.7746694638166</v>
+        <v>675.330223665419</v>
       </c>
       <c r="O4" t="n">
-        <v>26.09165900175412</v>
+        <v>25.9871164938594</v>
       </c>
       <c r="P4" t="n">
-        <v>381.4332742739264</v>
+        <v>381.3419415227667</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -27455,28 +27667,28 @@
         <v>0.0239</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8000278063574083</v>
+        <v>0.8149937411973684</v>
       </c>
       <c r="J5" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K5" t="n">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07919471812488699</v>
+        <v>0.08311841849823964</v>
       </c>
       <c r="M5" t="n">
-        <v>15.19658561872947</v>
+        <v>15.1459859267835</v>
       </c>
       <c r="N5" t="n">
-        <v>344.5950728747879</v>
+        <v>342.440529530157</v>
       </c>
       <c r="O5" t="n">
-        <v>18.56327214891782</v>
+        <v>18.50514873029009</v>
       </c>
       <c r="P5" t="n">
-        <v>353.9332743314175</v>
+        <v>353.7558355619022</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27533,28 +27745,28 @@
         <v>0.0308</v>
       </c>
       <c r="I6" t="n">
-        <v>0.322991597566656</v>
+        <v>0.3488662255853268</v>
       </c>
       <c r="J6" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K6" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02281517378479492</v>
+        <v>0.02674444491248729</v>
       </c>
       <c r="M6" t="n">
-        <v>11.69988593578091</v>
+        <v>11.72992588961241</v>
       </c>
       <c r="N6" t="n">
-        <v>201.902400059848</v>
+        <v>202.0435329307474</v>
       </c>
       <c r="O6" t="n">
-        <v>14.20923643479297</v>
+        <v>14.21420180420791</v>
       </c>
       <c r="P6" t="n">
-        <v>355.720273446511</v>
+        <v>355.4099104912023</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27611,28 +27823,28 @@
         <v>0.0359</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2496121263469235</v>
+        <v>0.2725751917712564</v>
       </c>
       <c r="J7" t="n">
+        <v>253</v>
+      </c>
+      <c r="K7" t="n">
         <v>251</v>
       </c>
-      <c r="K7" t="n">
-        <v>249</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.01876388208373025</v>
+        <v>0.02246805787948436</v>
       </c>
       <c r="M7" t="n">
-        <v>10.26717680031411</v>
+        <v>10.2686919633726</v>
       </c>
       <c r="N7" t="n">
-        <v>148.4204447019976</v>
+        <v>148.6520948483959</v>
       </c>
       <c r="O7" t="n">
-        <v>12.18279297624308</v>
+        <v>12.19229653709242</v>
       </c>
       <c r="P7" t="n">
-        <v>353.2196044399316</v>
+        <v>352.9456092724482</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27689,28 +27901,28 @@
         <v>0.0369</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1606872553367213</v>
+        <v>0.1837398153832878</v>
       </c>
       <c r="J8" t="n">
+        <v>253</v>
+      </c>
+      <c r="K8" t="n">
         <v>251</v>
       </c>
-      <c r="K8" t="n">
-        <v>249</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.01115627307823586</v>
+        <v>0.01459185758662518</v>
       </c>
       <c r="M8" t="n">
-        <v>8.297720471397213</v>
+        <v>8.322506335725866</v>
       </c>
       <c r="N8" t="n">
-        <v>104.2516483111329</v>
+        <v>104.8443600536295</v>
       </c>
       <c r="O8" t="n">
-        <v>10.21036964615547</v>
+        <v>10.23935349783518</v>
       </c>
       <c r="P8" t="n">
-        <v>353.3669198978601</v>
+        <v>353.0918554503001</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27767,28 +27979,28 @@
         <v>0.0422</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2138069250118314</v>
+        <v>0.2274385185766372</v>
       </c>
       <c r="J9" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K9" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02912369364073075</v>
+        <v>0.03315377191204905</v>
       </c>
       <c r="M9" t="n">
-        <v>6.75891465042635</v>
+        <v>6.765163441035174</v>
       </c>
       <c r="N9" t="n">
-        <v>69.97122172777307</v>
+        <v>69.92404706456394</v>
       </c>
       <c r="O9" t="n">
-        <v>8.364880257826353</v>
+        <v>8.362059977335964</v>
       </c>
       <c r="P9" t="n">
-        <v>352.829058662966</v>
+        <v>352.6672531541521</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27845,28 +28057,28 @@
         <v>0.045</v>
       </c>
       <c r="I10" t="n">
-        <v>0.28573624934641</v>
+        <v>0.2954606240658504</v>
       </c>
       <c r="J10" t="n">
+        <v>253</v>
+      </c>
+      <c r="K10" t="n">
         <v>251</v>
       </c>
-      <c r="K10" t="n">
-        <v>249</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.05497862473408111</v>
+        <v>0.05930002712863347</v>
       </c>
       <c r="M10" t="n">
-        <v>6.529817508082123</v>
+        <v>6.524271138561423</v>
       </c>
       <c r="N10" t="n">
-        <v>64.52911882537245</v>
+        <v>64.27782422295279</v>
       </c>
       <c r="O10" t="n">
-        <v>8.033001856427799</v>
+        <v>8.01734521041428</v>
       </c>
       <c r="P10" t="n">
-        <v>353.7816641561284</v>
+        <v>353.6661888781638</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27923,28 +28135,28 @@
         <v>0.0478</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3442978762367262</v>
+        <v>0.3508178568539466</v>
       </c>
       <c r="J11" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K11" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L11" t="n">
-        <v>0.08660584437208874</v>
+        <v>0.09087324975508837</v>
       </c>
       <c r="M11" t="n">
-        <v>6.209530252666155</v>
+        <v>6.192614070184347</v>
       </c>
       <c r="N11" t="n">
-        <v>57.40347570923051</v>
+        <v>57.07235827482127</v>
       </c>
       <c r="O11" t="n">
-        <v>7.576508147506376</v>
+        <v>7.554624959243263</v>
       </c>
       <c r="P11" t="n">
-        <v>355.9656326463019</v>
+        <v>355.8882547552466</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -28001,28 +28213,28 @@
         <v>0.0536</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2475701711083604</v>
+        <v>0.2493506675873849</v>
       </c>
       <c r="J12" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K12" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L12" t="n">
-        <v>0.06083211515054088</v>
+        <v>0.06264019733221182</v>
       </c>
       <c r="M12" t="n">
-        <v>5.224192377188697</v>
+        <v>5.193936967545985</v>
       </c>
       <c r="N12" t="n">
-        <v>43.4475631440711</v>
+        <v>43.12690951175423</v>
       </c>
       <c r="O12" t="n">
-        <v>6.591476552645173</v>
+        <v>6.567108154412734</v>
       </c>
       <c r="P12" t="n">
-        <v>363.7557010943711</v>
+        <v>363.7345983502507</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -28079,28 +28291,28 @@
         <v>0.0468</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2407396573844189</v>
+        <v>0.2430628462399494</v>
       </c>
       <c r="J13" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K13" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L13" t="n">
-        <v>0.06041876693970671</v>
+        <v>0.06248257865938645</v>
       </c>
       <c r="M13" t="n">
-        <v>5.312186179108162</v>
+        <v>5.283971938744018</v>
       </c>
       <c r="N13" t="n">
-        <v>41.38245253577153</v>
+        <v>41.08957214495185</v>
       </c>
       <c r="O13" t="n">
-        <v>6.432919441106932</v>
+        <v>6.410114830870961</v>
       </c>
       <c r="P13" t="n">
-        <v>372.0807238786096</v>
+        <v>372.0531837789104</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -28157,28 +28369,28 @@
         <v>0.0508</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1339284873380789</v>
+        <v>0.1312953260609926</v>
       </c>
       <c r="J14" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K14" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0244210342144896</v>
+        <v>0.02386713948077801</v>
       </c>
       <c r="M14" t="n">
-        <v>4.701264314491189</v>
+        <v>4.676180119914006</v>
       </c>
       <c r="N14" t="n">
-        <v>32.90052110571119</v>
+        <v>32.67993264446982</v>
       </c>
       <c r="O14" t="n">
-        <v>5.735897585008922</v>
+        <v>5.716636480000265</v>
       </c>
       <c r="P14" t="n">
-        <v>382.0911423890702</v>
+        <v>382.1224490746425</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -28235,28 +28447,28 @@
         <v>0.0555</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1245069555579758</v>
+        <v>0.1212478612606314</v>
       </c>
       <c r="J15" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K15" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02071783577265462</v>
+        <v>0.01998684764801228</v>
       </c>
       <c r="M15" t="n">
-        <v>4.721513151399819</v>
+        <v>4.698175043164268</v>
       </c>
       <c r="N15" t="n">
-        <v>33.64411894588145</v>
+        <v>33.41256635056164</v>
       </c>
       <c r="O15" t="n">
-        <v>5.800355070672954</v>
+        <v>5.780360399712257</v>
       </c>
       <c r="P15" t="n">
-        <v>376.7805973035142</v>
+        <v>376.8193172516662</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -28313,28 +28525,28 @@
         <v>0.0487</v>
       </c>
       <c r="I16" t="n">
-        <v>0.01493489626751607</v>
+        <v>0.01045580591917639</v>
       </c>
       <c r="J16" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K16" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0002428955396633903</v>
+        <v>0.0001209908231639689</v>
       </c>
       <c r="M16" t="n">
-        <v>5.366518408046066</v>
+        <v>5.341800428100027</v>
       </c>
       <c r="N16" t="n">
-        <v>42.21124195008922</v>
+        <v>41.93013891440673</v>
       </c>
       <c r="O16" t="n">
-        <v>6.497017927487135</v>
+        <v>6.475348555437517</v>
       </c>
       <c r="P16" t="n">
-        <v>377.3840284788789</v>
+        <v>377.4373124395223</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -28391,28 +28603,28 @@
         <v>0.0534</v>
       </c>
       <c r="I17" t="n">
-        <v>0.04020146575433275</v>
+        <v>0.0405078948049172</v>
       </c>
       <c r="J17" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K17" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L17" t="n">
-        <v>0.001662017744166078</v>
+        <v>0.0017163959462001</v>
       </c>
       <c r="M17" t="n">
-        <v>5.256976909457275</v>
+        <v>5.225849358555018</v>
       </c>
       <c r="N17" t="n">
-        <v>44.63488951224173</v>
+        <v>44.29269033241999</v>
       </c>
       <c r="O17" t="n">
-        <v>6.68093477832569</v>
+        <v>6.655275376152364</v>
       </c>
       <c r="P17" t="n">
-        <v>375.2674235778754</v>
+        <v>375.2638151273416</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -28469,28 +28681,28 @@
         <v>0.0579</v>
       </c>
       <c r="I18" t="n">
-        <v>0.06192184478542932</v>
+        <v>0.05693157867205486</v>
       </c>
       <c r="J18" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K18" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L18" t="n">
-        <v>0.004450100684913472</v>
+        <v>0.003822776060237287</v>
       </c>
       <c r="M18" t="n">
-        <v>5.169826897445415</v>
+        <v>5.147561339233987</v>
       </c>
       <c r="N18" t="n">
-        <v>39.38577919970044</v>
+        <v>39.15058559617505</v>
       </c>
       <c r="O18" t="n">
-        <v>6.27580904742173</v>
+        <v>6.257042879521848</v>
       </c>
       <c r="P18" t="n">
-        <v>375.8625252026371</v>
+        <v>375.9218055065502</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -28547,28 +28759,28 @@
         <v>0.053</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1011585055120086</v>
+        <v>0.1043720185040802</v>
       </c>
       <c r="J19" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K19" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="L19" t="n">
-        <v>0.01064615815596182</v>
+        <v>0.01151253799030139</v>
       </c>
       <c r="M19" t="n">
-        <v>5.413862667657759</v>
+        <v>5.386777778246717</v>
       </c>
       <c r="N19" t="n">
-        <v>44.00602511964394</v>
+        <v>43.69452580323478</v>
       </c>
       <c r="O19" t="n">
-        <v>6.633703725645572</v>
+        <v>6.610183492402823</v>
       </c>
       <c r="P19" t="n">
-        <v>379.5800719600987</v>
+        <v>379.5421424633608</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -28625,28 +28837,28 @@
         <v>0.049</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0750741076747956</v>
+        <v>0.07692528911751338</v>
       </c>
       <c r="J20" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K20" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L20" t="n">
-        <v>0.005979681807700032</v>
+        <v>0.006383460224091309</v>
       </c>
       <c r="M20" t="n">
-        <v>5.139366246694038</v>
+        <v>5.10907593408612</v>
       </c>
       <c r="N20" t="n">
-        <v>42.33539767247147</v>
+        <v>42.01793722834498</v>
       </c>
       <c r="O20" t="n">
-        <v>6.506565735660516</v>
+        <v>6.482124437894183</v>
       </c>
       <c r="P20" t="n">
-        <v>384.7492542611178</v>
+        <v>384.7270788764642</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -28703,28 +28915,28 @@
         <v>0.0506</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2029370012484338</v>
+        <v>0.2059910642930824</v>
       </c>
       <c r="J21" t="n">
+        <v>253</v>
+      </c>
+      <c r="K21" t="n">
         <v>251</v>
       </c>
-      <c r="K21" t="n">
-        <v>249</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.04351991914863385</v>
+        <v>0.04548234394240736</v>
       </c>
       <c r="M21" t="n">
-        <v>4.945494032367912</v>
+        <v>4.922790443831827</v>
       </c>
       <c r="N21" t="n">
-        <v>41.23080989231283</v>
+        <v>40.95159756601225</v>
       </c>
       <c r="O21" t="n">
-        <v>6.421122167683219</v>
+        <v>6.399343526176123</v>
       </c>
       <c r="P21" t="n">
-        <v>388.2453498989753</v>
+        <v>388.2089475637957</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -28781,28 +28993,28 @@
         <v>0.057</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1502082546983211</v>
+        <v>0.1589551491814263</v>
       </c>
       <c r="J22" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K22" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="L22" t="n">
-        <v>0.03071635896115521</v>
+        <v>0.03461532866292949</v>
       </c>
       <c r="M22" t="n">
-        <v>4.407140786260808</v>
+        <v>4.418141220092462</v>
       </c>
       <c r="N22" t="n">
-        <v>32.94711190810649</v>
+        <v>32.91849092628991</v>
       </c>
       <c r="O22" t="n">
-        <v>5.739957483127073</v>
+        <v>5.737463806098467</v>
       </c>
       <c r="P22" t="n">
-        <v>387.3839087492571</v>
+        <v>387.2806422947892</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -28859,28 +29071,28 @@
         <v>0.0611</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1885111349704542</v>
+        <v>0.1955870759104925</v>
       </c>
       <c r="J23" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K23" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="L23" t="n">
-        <v>0.04652623541313172</v>
+        <v>0.05051943235718082</v>
       </c>
       <c r="M23" t="n">
-        <v>4.436277830013648</v>
+        <v>4.437217071340778</v>
       </c>
       <c r="N23" t="n">
-        <v>33.70027559835815</v>
+        <v>33.58665111446729</v>
       </c>
       <c r="O23" t="n">
-        <v>5.805193846751213</v>
+        <v>5.795399133318369</v>
       </c>
       <c r="P23" t="n">
-        <v>385.3708026998889</v>
+        <v>385.287264763366</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -28937,28 +29149,28 @@
         <v>0.064</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2450287548506633</v>
+        <v>0.2544988144520209</v>
       </c>
       <c r="J24" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K24" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L24" t="n">
-        <v>0.06459239102959968</v>
+        <v>0.07003361741895875</v>
       </c>
       <c r="M24" t="n">
-        <v>5.017257150323927</v>
+        <v>5.017962812059035</v>
       </c>
       <c r="N24" t="n">
-        <v>40.29454687256938</v>
+        <v>40.23536964656623</v>
       </c>
       <c r="O24" t="n">
-        <v>6.347798584751203</v>
+        <v>6.343135632048729</v>
       </c>
       <c r="P24" t="n">
-        <v>383.8560608630766</v>
+        <v>383.7441986778575</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -29015,28 +29227,28 @@
         <v>0.0766</v>
       </c>
       <c r="I25" t="n">
-        <v>0.18774774044718</v>
+        <v>0.1987788749925458</v>
       </c>
       <c r="J25" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K25" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="L25" t="n">
-        <v>0.05645664509766957</v>
+        <v>0.06315703317088472</v>
       </c>
       <c r="M25" t="n">
-        <v>4.141976093418699</v>
+        <v>4.157027121227041</v>
       </c>
       <c r="N25" t="n">
-        <v>27.26119150613868</v>
+        <v>27.38068527850042</v>
       </c>
       <c r="O25" t="n">
-        <v>5.221225096290973</v>
+        <v>5.232655662137574</v>
       </c>
       <c r="P25" t="n">
-        <v>377.7761273532345</v>
+        <v>377.6458621306713</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -29093,28 +29305,28 @@
         <v>0.0496</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1323250803001057</v>
+        <v>0.1441213553155795</v>
       </c>
       <c r="J26" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K26" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="L26" t="n">
-        <v>0.02142856094171797</v>
+        <v>0.02549494368203542</v>
       </c>
       <c r="M26" t="n">
-        <v>4.586312212608749</v>
+        <v>4.607665236128331</v>
       </c>
       <c r="N26" t="n">
-        <v>37.00261902708647</v>
+        <v>37.08903139650894</v>
       </c>
       <c r="O26" t="n">
-        <v>6.082977809189054</v>
+        <v>6.090076468855621</v>
       </c>
       <c r="P26" t="n">
-        <v>383.213259405981</v>
+        <v>383.0739528633703</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -29171,28 +29383,28 @@
         <v>0.0752</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1717728673883384</v>
+        <v>0.1845094915192203</v>
       </c>
       <c r="J27" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K27" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="L27" t="n">
-        <v>0.05091291314239577</v>
+        <v>0.05826700403838447</v>
       </c>
       <c r="M27" t="n">
-        <v>3.842490427528412</v>
+        <v>3.878099482693387</v>
       </c>
       <c r="N27" t="n">
-        <v>25.45281671483618</v>
+        <v>25.70403474919681</v>
       </c>
       <c r="O27" t="n">
-        <v>5.045078464685775</v>
+        <v>5.069914668827949</v>
       </c>
       <c r="P27" t="n">
-        <v>367.1422460127793</v>
+        <v>366.9918472664395</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -29249,28 +29461,28 @@
         <v>0.0784</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1560396964930587</v>
+        <v>0.1710092489078192</v>
       </c>
       <c r="J28" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K28" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L28" t="n">
-        <v>0.03155115944820375</v>
+        <v>0.03765202214180507</v>
       </c>
       <c r="M28" t="n">
-        <v>4.570866565676692</v>
+        <v>4.599034515617997</v>
       </c>
       <c r="N28" t="n">
-        <v>34.54042358024453</v>
+        <v>34.8713396392971</v>
       </c>
       <c r="O28" t="n">
-        <v>5.877110138515742</v>
+        <v>5.905195986527213</v>
       </c>
       <c r="P28" t="n">
-        <v>363.6251303309132</v>
+        <v>363.4479997673228</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -29327,28 +29539,28 @@
         <v>0.1741</v>
       </c>
       <c r="I29" t="n">
-        <v>0.007584734782068776</v>
+        <v>0.01843949224727162</v>
       </c>
       <c r="J29" t="n">
+        <v>253</v>
+      </c>
+      <c r="K29" t="n">
         <v>251</v>
       </c>
-      <c r="K29" t="n">
-        <v>249</v>
-      </c>
       <c r="L29" t="n">
-        <v>0.0001010794667971604</v>
+        <v>0.0006003288294751385</v>
       </c>
       <c r="M29" t="n">
-        <v>3.896575430807054</v>
+        <v>3.909104911372391</v>
       </c>
       <c r="N29" t="n">
-        <v>26.37387863235298</v>
+        <v>26.47952539792698</v>
       </c>
       <c r="O29" t="n">
-        <v>5.135550470237146</v>
+        <v>5.145826017067326</v>
       </c>
       <c r="P29" t="n">
-        <v>371.9440563462746</v>
+        <v>371.8156521051873</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -29386,7 +29598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD252"/>
+  <dimension ref="A1:AD254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67289,6 +67501,310 @@
         </is>
       </c>
     </row>
+    <row r="253">
+      <c r="A253" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>-35.631981664109304,174.51509087539296</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>-35.63274915255711,174.5149729955636</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>-35.63338053920866,174.51451762971445</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>-35.633993237831675,174.51395516784515</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>-35.63455479968218,174.51333663481896</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>-35.635052519788466,174.5126647906289</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>-35.63556674861058,174.51202633887158</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>-35.63606251387157,174.5113640630496</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>-35.63659585716952,174.5107511183622</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>-35.63713991179602,174.5101521082093</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>-35.63768877145179,174.50955940462296</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>-35.63827134124744,174.5090191264275</t>
+        </is>
+      </c>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>-35.63882774422629,174.50849478581125</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>-35.63942293993551,174.50801622600935</t>
+        </is>
+      </c>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>-35.640051583175875,174.50755737652096</t>
+        </is>
+      </c>
+      <c r="Q253" t="inlineStr">
+        <is>
+          <t>-35.640704275415935,174.50714969305216</t>
+        </is>
+      </c>
+      <c r="R253" t="inlineStr">
+        <is>
+          <t>-35.64133106374545,174.50668102685154</t>
+        </is>
+      </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>-35.641999886176656,174.50630433646327</t>
+        </is>
+      </c>
+      <c r="T253" t="inlineStr">
+        <is>
+          <t>-35.64264209319545,174.50587580375364</t>
+        </is>
+      </c>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>-35.64329222028045,174.50549520456406</t>
+        </is>
+      </c>
+      <c r="V253" t="inlineStr">
+        <is>
+          <t>-35.643935074088716,174.50511717690515</t>
+        </is>
+      </c>
+      <c r="W253" t="inlineStr">
+        <is>
+          <t>-35.64458432476109,174.5047152654709</t>
+        </is>
+      </c>
+      <c r="X253" t="inlineStr">
+        <is>
+          <t>-35.645235387374576,174.50435671350047</t>
+        </is>
+      </c>
+      <c r="Y253" t="inlineStr">
+        <is>
+          <t>-35.64588748447592,174.5039969364386</t>
+        </is>
+      </c>
+      <c r="Z253" t="inlineStr">
+        <is>
+          <t>-35.64659087622088,174.50376099528913</t>
+        </is>
+      </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>-35.64724610718854,174.5033333069113</t>
+        </is>
+      </c>
+      <c r="AB253" t="inlineStr">
+        <is>
+          <t>-35.64792263977419,174.50302039688856</t>
+        </is>
+      </c>
+      <c r="AC253" t="inlineStr">
+        <is>
+          <t>-35.64862856819134,174.5028595436182</t>
+        </is>
+      </c>
+      <c r="AD253" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>-35.631981664109304,174.51509087539296</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>-35.63274915255711,174.5149729955636</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>-35.63334077587492,174.51441902596184</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>-35.63398048009676,174.51393055967245</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>-35.634532627687385,174.51330523200085</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>-35.63502560799474,174.51262955217908</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>-35.635540329361355,174.51199174542475</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>-35.63604405325948,174.51133970430618</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>-35.63658060809095,174.51073079205455</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>-35.63712492666167,174.51013208454057</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>-35.63767171513076,174.50953661337294</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>-35.6382520599269,174.50899210602313</t>
+        </is>
+      </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>-35.63881096647604,174.50846402762897</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>-35.639414758480584,174.50799716716043</t>
+        </is>
+      </c>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>-35.64004591905973,174.5075441818483</t>
+        </is>
+      </c>
+      <c r="Q254" t="inlineStr">
+        <is>
+          <t>-35.64069266184654,174.5071234902819</t>
+        </is>
+      </c>
+      <c r="R254" t="inlineStr">
+        <is>
+          <t>-35.64132004813784,174.50665757703422</t>
+        </is>
+      </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>-35.64199025673021,174.50628437038964</t>
+        </is>
+      </c>
+      <c r="T254" t="inlineStr">
+        <is>
+          <t>-35.642630721228436,174.5058522246153</t>
+        </is>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>-35.6432772353906,174.50546093987577</t>
+        </is>
+      </c>
+      <c r="V254" t="inlineStr">
+        <is>
+          <t>-35.64392076027826,174.50507978190006</t>
+        </is>
+      </c>
+      <c r="W254" t="inlineStr">
+        <is>
+          <t>-35.644572752120816,174.50468410425228</t>
+        </is>
+      </c>
+      <c r="X254" t="inlineStr">
+        <is>
+          <t>-35.64522478254874,174.50432361143078</t>
+        </is>
+      </c>
+      <c r="Y254" t="inlineStr">
+        <is>
+          <t>-35.64588101240106,174.50397257286585</t>
+        </is>
+      </c>
+      <c r="Z254" t="inlineStr">
+        <is>
+          <t>-35.64658532404077,174.50373963324088</t>
+        </is>
+      </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>-35.64723743694709,174.50329994819995</t>
+        </is>
+      </c>
+      <c r="AB254" t="inlineStr">
+        <is>
+          <t>-35.64791809619574,174.50299845175172</t>
+        </is>
+      </c>
+      <c r="AC254" t="inlineStr">
+        <is>
+          <t>-35.64862748854058,174.50285260028946</t>
+        </is>
+      </c>
+      <c r="AD254" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0094/nzd0094.xlsx
+++ b/data/nzd0094/nzd0094.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD254"/>
+  <dimension ref="A1:AD255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24669,6 +24669,102 @@
         </is>
       </c>
     </row>
+    <row r="255">
+      <c r="A255" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>378.81</v>
+      </c>
+      <c r="C255" t="n">
+        <v>409.63</v>
+      </c>
+      <c r="D255" t="n">
+        <v>390.26</v>
+      </c>
+      <c r="E255" t="n">
+        <v>381.24</v>
+      </c>
+      <c r="F255" t="n">
+        <v>375.38</v>
+      </c>
+      <c r="G255" t="n">
+        <v>367.64</v>
+      </c>
+      <c r="H255" t="n">
+        <v>365.53</v>
+      </c>
+      <c r="I255" t="n">
+        <v>362.92</v>
+      </c>
+      <c r="J255" t="n">
+        <v>364.12</v>
+      </c>
+      <c r="K255" t="n">
+        <v>366.21</v>
+      </c>
+      <c r="L255" t="n">
+        <v>368.75</v>
+      </c>
+      <c r="M255" t="n">
+        <v>377.29</v>
+      </c>
+      <c r="N255" t="n">
+        <v>380.97</v>
+      </c>
+      <c r="O255" t="n">
+        <v>375.91</v>
+      </c>
+      <c r="P255" t="n">
+        <v>372.53</v>
+      </c>
+      <c r="Q255" t="n">
+        <v>373.71</v>
+      </c>
+      <c r="R255" t="n">
+        <v>371.82</v>
+      </c>
+      <c r="S255" t="n">
+        <v>381.56</v>
+      </c>
+      <c r="T255" t="n">
+        <v>384.02</v>
+      </c>
+      <c r="U255" t="n">
+        <v>391.45</v>
+      </c>
+      <c r="V255" t="n">
+        <v>391.3</v>
+      </c>
+      <c r="W255" t="n">
+        <v>390.44</v>
+      </c>
+      <c r="X255" t="n">
+        <v>392.53</v>
+      </c>
+      <c r="Y255" t="n">
+        <v>385.94</v>
+      </c>
+      <c r="Z255" t="n">
+        <v>389.87</v>
+      </c>
+      <c r="AA255" t="n">
+        <v>375.43</v>
+      </c>
+      <c r="AB255" t="n">
+        <v>371.7</v>
+      </c>
+      <c r="AC255" t="n">
+        <v>376.14</v>
+      </c>
+      <c r="AD255" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24680,7 +24776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B257"/>
+  <dimension ref="A1:B258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27253,6 +27349,16 @@
       </c>
       <c r="B257" t="n">
         <v>-0.63</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>0.17</v>
       </c>
     </row>
   </sheetData>
@@ -27421,28 +27527,28 @@
         <v>0.0102</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9628084309279903</v>
+        <v>0.9480261921337116</v>
       </c>
       <c r="J2" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K2" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03547530437611879</v>
+        <v>0.0346939452363505</v>
       </c>
       <c r="M2" t="n">
-        <v>26.62345235630442</v>
+        <v>26.56946808255524</v>
       </c>
       <c r="N2" t="n">
-        <v>1102.942060035547</v>
+        <v>1099.309630576039</v>
       </c>
       <c r="O2" t="n">
-        <v>33.21057151022166</v>
+        <v>33.15583855938557</v>
       </c>
       <c r="P2" t="n">
-        <v>369.1987644395404</v>
+        <v>369.3833240556464</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -27503,28 +27609,28 @@
         <v>0.0104</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8754918685113454</v>
+        <v>0.8779933608934187</v>
       </c>
       <c r="J3" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K3" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04522085982224278</v>
+        <v>0.04584124017162494</v>
       </c>
       <c r="M3" t="n">
-        <v>22.07243802779213</v>
+        <v>21.9904083584418</v>
       </c>
       <c r="N3" t="n">
-        <v>756.0911567557039</v>
+        <v>752.7795538311881</v>
       </c>
       <c r="O3" t="n">
-        <v>27.49711178934442</v>
+        <v>27.43682842150652</v>
       </c>
       <c r="P3" t="n">
-        <v>383.5474185371847</v>
+        <v>383.5169854877785</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -27585,28 +27691,28 @@
         <v>0.0106</v>
       </c>
       <c r="I4" t="n">
-        <v>0.357325545695202</v>
+        <v>0.3567850162282836</v>
       </c>
       <c r="J4" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K4" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008319954348276148</v>
+        <v>0.008368326894605649</v>
       </c>
       <c r="M4" t="n">
-        <v>21.20120079221915</v>
+        <v>21.11313682051342</v>
       </c>
       <c r="N4" t="n">
-        <v>675.330223665419</v>
+        <v>672.4701159114309</v>
       </c>
       <c r="O4" t="n">
-        <v>25.9871164938594</v>
+        <v>25.93202876582222</v>
       </c>
       <c r="P4" t="n">
-        <v>381.3419415227667</v>
+        <v>381.3486207726558</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -27667,28 +27773,28 @@
         <v>0.0239</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8149937411973684</v>
+        <v>0.8199459392677685</v>
       </c>
       <c r="J5" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K5" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08311841849823964</v>
+        <v>0.08468294725735703</v>
       </c>
       <c r="M5" t="n">
-        <v>15.1459859267835</v>
+        <v>15.10869722996832</v>
       </c>
       <c r="N5" t="n">
-        <v>342.440529530157</v>
+        <v>341.2036335295632</v>
       </c>
       <c r="O5" t="n">
-        <v>18.50514873029009</v>
+        <v>18.47169817665834</v>
       </c>
       <c r="P5" t="n">
-        <v>353.7558355619022</v>
+        <v>353.6968821082139</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27745,28 +27851,28 @@
         <v>0.0308</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3488662255853268</v>
+        <v>0.3581353683282698</v>
       </c>
       <c r="J6" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K6" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02674444491248729</v>
+        <v>0.0283220128357462</v>
       </c>
       <c r="M6" t="n">
-        <v>11.72992588961241</v>
+        <v>11.72695582223928</v>
       </c>
       <c r="N6" t="n">
-        <v>202.0435329307474</v>
+        <v>201.6881422196574</v>
       </c>
       <c r="O6" t="n">
-        <v>14.21420180420791</v>
+        <v>14.20169504741098</v>
       </c>
       <c r="P6" t="n">
-        <v>355.4099104912023</v>
+        <v>355.298290683938</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27823,28 +27929,28 @@
         <v>0.0359</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2725751917712564</v>
+        <v>0.2789782646970732</v>
       </c>
       <c r="J7" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K7" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02246805787948436</v>
+        <v>0.02367760851506617</v>
       </c>
       <c r="M7" t="n">
-        <v>10.2686919633726</v>
+        <v>10.25113288872826</v>
       </c>
       <c r="N7" t="n">
-        <v>148.6520948483959</v>
+        <v>148.2790505990998</v>
       </c>
       <c r="O7" t="n">
-        <v>12.19229653709242</v>
+        <v>12.17698856857063</v>
       </c>
       <c r="P7" t="n">
-        <v>352.9456092724482</v>
+        <v>352.8689022506594</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27901,28 +28007,28 @@
         <v>0.0369</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1837398153832878</v>
+        <v>0.1902369316541769</v>
       </c>
       <c r="J8" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K8" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01459185758662518</v>
+        <v>0.01572690152989553</v>
       </c>
       <c r="M8" t="n">
-        <v>8.322506335725866</v>
+        <v>8.315355297405029</v>
       </c>
       <c r="N8" t="n">
-        <v>104.8443600536295</v>
+        <v>104.6515724995811</v>
       </c>
       <c r="O8" t="n">
-        <v>10.23935349783518</v>
+        <v>10.22993511707582</v>
       </c>
       <c r="P8" t="n">
-        <v>353.0918554503001</v>
+        <v>353.0140218155548</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27979,28 +28085,28 @@
         <v>0.0422</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2274385185766372</v>
+        <v>0.2310300965572099</v>
       </c>
       <c r="J9" t="n">
+        <v>254</v>
+      </c>
+      <c r="K9" t="n">
         <v>253</v>
       </c>
-      <c r="K9" t="n">
-        <v>252</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.03315377191204905</v>
+        <v>0.03442765256076918</v>
       </c>
       <c r="M9" t="n">
-        <v>6.765163441035174</v>
+        <v>6.753985089700988</v>
       </c>
       <c r="N9" t="n">
-        <v>69.92404706456394</v>
+        <v>69.71661467961637</v>
       </c>
       <c r="O9" t="n">
-        <v>8.362059977335964</v>
+        <v>8.349647578168577</v>
       </c>
       <c r="P9" t="n">
-        <v>352.6672531541521</v>
+        <v>352.6244489986059</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -28057,28 +28163,28 @@
         <v>0.045</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2954606240658504</v>
+        <v>0.2976769148822173</v>
       </c>
       <c r="J10" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K10" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05930002712863347</v>
+        <v>0.06060724890218316</v>
       </c>
       <c r="M10" t="n">
-        <v>6.524271138561423</v>
+        <v>6.50881745885988</v>
       </c>
       <c r="N10" t="n">
-        <v>64.27782422295279</v>
+        <v>64.04908880060236</v>
       </c>
       <c r="O10" t="n">
-        <v>8.01734521041428</v>
+        <v>8.00306746195497</v>
       </c>
       <c r="P10" t="n">
-        <v>353.6661888781638</v>
+        <v>353.6397626372006</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -28135,28 +28241,28 @@
         <v>0.0478</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3508178568539466</v>
+        <v>0.3516602540246593</v>
       </c>
       <c r="J11" t="n">
+        <v>254</v>
+      </c>
+      <c r="K11" t="n">
         <v>253</v>
       </c>
-      <c r="K11" t="n">
-        <v>252</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.09087324975508837</v>
+        <v>0.09198683278752573</v>
       </c>
       <c r="M11" t="n">
-        <v>6.192614070184347</v>
+        <v>6.172255156589274</v>
       </c>
       <c r="N11" t="n">
-        <v>57.07235827482127</v>
+        <v>56.85056880738077</v>
       </c>
       <c r="O11" t="n">
-        <v>7.554624959243263</v>
+        <v>7.539931618216492</v>
       </c>
       <c r="P11" t="n">
-        <v>355.8882547552466</v>
+        <v>355.8782151292878</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -28213,28 +28319,28 @@
         <v>0.0536</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2493506675873849</v>
+        <v>0.2479624285779731</v>
       </c>
       <c r="J12" t="n">
+        <v>254</v>
+      </c>
+      <c r="K12" t="n">
         <v>253</v>
       </c>
-      <c r="K12" t="n">
-        <v>252</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.06264019733221182</v>
+        <v>0.06248007524222898</v>
       </c>
       <c r="M12" t="n">
-        <v>5.193936967545985</v>
+        <v>5.179727229994197</v>
       </c>
       <c r="N12" t="n">
-        <v>43.12690951175423</v>
+        <v>42.96674831053164</v>
       </c>
       <c r="O12" t="n">
-        <v>6.567108154412734</v>
+        <v>6.554902616403362</v>
       </c>
       <c r="P12" t="n">
-        <v>363.7345983502507</v>
+        <v>363.7511432780834</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -28291,28 +28397,28 @@
         <v>0.0468</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2430628462399494</v>
+        <v>0.2420080191724348</v>
       </c>
       <c r="J13" t="n">
+        <v>254</v>
+      </c>
+      <c r="K13" t="n">
         <v>253</v>
       </c>
-      <c r="K13" t="n">
-        <v>252</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.06248257865938645</v>
+        <v>0.06247272453851405</v>
       </c>
       <c r="M13" t="n">
-        <v>5.283971938744018</v>
+        <v>5.267468114494553</v>
       </c>
       <c r="N13" t="n">
-        <v>41.08957214495185</v>
+        <v>40.9331099185066</v>
       </c>
       <c r="O13" t="n">
-        <v>6.410114830870961</v>
+        <v>6.39789886748037</v>
       </c>
       <c r="P13" t="n">
-        <v>372.0531837789104</v>
+        <v>372.0657551283608</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -28369,28 +28475,28 @@
         <v>0.0508</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1312953260609926</v>
+        <v>0.1273284834452958</v>
       </c>
       <c r="J14" t="n">
+        <v>254</v>
+      </c>
+      <c r="K14" t="n">
         <v>253</v>
       </c>
-      <c r="K14" t="n">
-        <v>252</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.02386713948077801</v>
+        <v>0.02261296815312608</v>
       </c>
       <c r="M14" t="n">
-        <v>4.676180119914006</v>
+        <v>4.674605567032124</v>
       </c>
       <c r="N14" t="n">
-        <v>32.67993264446982</v>
+        <v>32.63487075039418</v>
       </c>
       <c r="O14" t="n">
-        <v>5.716636480000265</v>
+        <v>5.712693826067889</v>
       </c>
       <c r="P14" t="n">
-        <v>382.1224490746425</v>
+        <v>382.169725605813</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -28447,28 +28553,28 @@
         <v>0.0555</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1212478612606314</v>
+        <v>0.1177111598986947</v>
       </c>
       <c r="J15" t="n">
+        <v>254</v>
+      </c>
+      <c r="K15" t="n">
         <v>253</v>
       </c>
-      <c r="K15" t="n">
-        <v>252</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.01998684764801228</v>
+        <v>0.01898331320381441</v>
       </c>
       <c r="M15" t="n">
-        <v>4.698175043164268</v>
+        <v>4.694906863921569</v>
       </c>
       <c r="N15" t="n">
-        <v>33.41256635056164</v>
+        <v>33.34735729024792</v>
       </c>
       <c r="O15" t="n">
-        <v>5.780360399712257</v>
+        <v>5.774717074476283</v>
       </c>
       <c r="P15" t="n">
-        <v>376.8193172516662</v>
+        <v>376.8614673918095</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -28525,28 +28631,28 @@
         <v>0.0487</v>
       </c>
       <c r="I16" t="n">
-        <v>0.01045580591917639</v>
+        <v>0.006011932274049773</v>
       </c>
       <c r="J16" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K16" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0001209908231639689</v>
+        <v>4.024925617407416e-05</v>
       </c>
       <c r="M16" t="n">
-        <v>5.341800428100027</v>
+        <v>5.338343207855274</v>
       </c>
       <c r="N16" t="n">
-        <v>41.93013891440673</v>
+        <v>41.86904706355716</v>
       </c>
       <c r="O16" t="n">
-        <v>6.475348555437517</v>
+        <v>6.470629572426254</v>
       </c>
       <c r="P16" t="n">
-        <v>377.4373124395223</v>
+        <v>377.4903626330483</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -28603,28 +28709,28 @@
         <v>0.0534</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0405078948049172</v>
+        <v>0.0382580452739861</v>
       </c>
       <c r="J17" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K17" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0017163959462001</v>
+        <v>0.001543651493357445</v>
       </c>
       <c r="M17" t="n">
-        <v>5.225849358555018</v>
+        <v>5.214538877341272</v>
       </c>
       <c r="N17" t="n">
-        <v>44.29269033241999</v>
+        <v>44.14338529048617</v>
       </c>
       <c r="O17" t="n">
-        <v>6.655275376152364</v>
+        <v>6.644048862740714</v>
       </c>
       <c r="P17" t="n">
-        <v>375.2638151273416</v>
+        <v>375.2906734411803</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -28681,28 +28787,28 @@
         <v>0.0579</v>
       </c>
       <c r="I18" t="n">
-        <v>0.05693157867205486</v>
+        <v>0.05213063008365649</v>
       </c>
       <c r="J18" t="n">
+        <v>254</v>
+      </c>
+      <c r="K18" t="n">
         <v>253</v>
       </c>
-      <c r="K18" t="n">
-        <v>252</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.003822776060237287</v>
+        <v>0.0032249035603924</v>
       </c>
       <c r="M18" t="n">
-        <v>5.147561339233987</v>
+        <v>5.145051102908715</v>
       </c>
       <c r="N18" t="n">
-        <v>39.15058559617505</v>
+        <v>39.11903728707962</v>
       </c>
       <c r="O18" t="n">
-        <v>6.257042879521848</v>
+        <v>6.254521347559669</v>
       </c>
       <c r="P18" t="n">
-        <v>375.9218055065502</v>
+        <v>375.9790228498068</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -28759,28 +28865,28 @@
         <v>0.053</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1043720185040802</v>
+        <v>0.1037286743950108</v>
       </c>
       <c r="J19" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K19" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L19" t="n">
-        <v>0.01151253799030139</v>
+        <v>0.01146978228491347</v>
       </c>
       <c r="M19" t="n">
-        <v>5.386777778246717</v>
+        <v>5.368360417489096</v>
       </c>
       <c r="N19" t="n">
-        <v>43.69452580323478</v>
+        <v>43.52473534408453</v>
       </c>
       <c r="O19" t="n">
-        <v>6.610183492402823</v>
+        <v>6.597327894237524</v>
       </c>
       <c r="P19" t="n">
-        <v>379.5421424633608</v>
+        <v>379.5497703922748</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -28837,28 +28943,28 @@
         <v>0.049</v>
       </c>
       <c r="I20" t="n">
-        <v>0.07692528911751338</v>
+        <v>0.07453724047056365</v>
       </c>
       <c r="J20" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K20" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L20" t="n">
-        <v>0.006383460224091309</v>
+        <v>0.006043535978439207</v>
       </c>
       <c r="M20" t="n">
-        <v>5.10907593408612</v>
+        <v>5.098413267629843</v>
       </c>
       <c r="N20" t="n">
-        <v>42.01793722834498</v>
+        <v>41.88037505524304</v>
       </c>
       <c r="O20" t="n">
-        <v>6.482124437894183</v>
+        <v>6.471504852446843</v>
       </c>
       <c r="P20" t="n">
-        <v>384.7270788764642</v>
+        <v>384.7558359618931</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -28915,28 +29021,28 @@
         <v>0.0506</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2059910642930824</v>
+        <v>0.2040623973044895</v>
       </c>
       <c r="J21" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K21" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L21" t="n">
-        <v>0.04548234394240736</v>
+        <v>0.04502444989493792</v>
       </c>
       <c r="M21" t="n">
-        <v>4.922790443831827</v>
+        <v>4.910325471629938</v>
       </c>
       <c r="N21" t="n">
-        <v>40.95159756601225</v>
+        <v>40.80876497167229</v>
       </c>
       <c r="O21" t="n">
-        <v>6.399343526176123</v>
+        <v>6.388173836995381</v>
       </c>
       <c r="P21" t="n">
-        <v>388.2089475637957</v>
+        <v>388.2320524545929</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -28993,28 +29099,28 @@
         <v>0.057</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1589551491814263</v>
+        <v>0.1587735153367046</v>
       </c>
       <c r="J22" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K22" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L22" t="n">
-        <v>0.03461532866292949</v>
+        <v>0.03482853604415814</v>
       </c>
       <c r="M22" t="n">
-        <v>4.418141220092462</v>
+        <v>4.401454520835079</v>
       </c>
       <c r="N22" t="n">
-        <v>32.91849092628991</v>
+        <v>32.78906873630751</v>
       </c>
       <c r="O22" t="n">
-        <v>5.737463806098467</v>
+        <v>5.726174005067215</v>
       </c>
       <c r="P22" t="n">
-        <v>387.2806422947892</v>
+        <v>387.282795870203</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -29071,28 +29177,28 @@
         <v>0.0611</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1955870759104925</v>
+        <v>0.1955385354308922</v>
       </c>
       <c r="J23" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K23" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L23" t="n">
-        <v>0.05051943235718082</v>
+        <v>0.05091211970234089</v>
       </c>
       <c r="M23" t="n">
-        <v>4.437217071340778</v>
+        <v>4.419949279257911</v>
       </c>
       <c r="N23" t="n">
-        <v>33.58665111446729</v>
+        <v>33.45443292917155</v>
       </c>
       <c r="O23" t="n">
-        <v>5.795399133318369</v>
+        <v>5.783980716528328</v>
       </c>
       <c r="P23" t="n">
-        <v>385.287264763366</v>
+        <v>385.2878402925775</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -29149,28 +29255,28 @@
         <v>0.064</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2544988144520209</v>
+        <v>0.2562103584478388</v>
       </c>
       <c r="J24" t="n">
+        <v>254</v>
+      </c>
+      <c r="K24" t="n">
         <v>253</v>
       </c>
-      <c r="K24" t="n">
-        <v>252</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.07003361741895875</v>
+        <v>0.07145669875869087</v>
       </c>
       <c r="M24" t="n">
-        <v>5.017962812059035</v>
+        <v>5.005480675901071</v>
       </c>
       <c r="N24" t="n">
-        <v>40.23536964656623</v>
+        <v>40.09220654783431</v>
       </c>
       <c r="O24" t="n">
-        <v>6.343135632048729</v>
+        <v>6.331840691918449</v>
       </c>
       <c r="P24" t="n">
-        <v>383.7441986778575</v>
+        <v>383.7238963912124</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -29227,28 +29333,28 @@
         <v>0.0766</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1987788749925458</v>
+        <v>0.201332093751014</v>
       </c>
       <c r="J25" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K25" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L25" t="n">
-        <v>0.06315703317088472</v>
+        <v>0.06513119188369676</v>
       </c>
       <c r="M25" t="n">
-        <v>4.157027121227041</v>
+        <v>4.152327882544828</v>
       </c>
       <c r="N25" t="n">
-        <v>27.38068527850042</v>
+        <v>27.30809294094619</v>
       </c>
       <c r="O25" t="n">
-        <v>5.232655662137574</v>
+        <v>5.225714586632741</v>
       </c>
       <c r="P25" t="n">
-        <v>377.6458621306713</v>
+        <v>377.6155894182664</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -29305,28 +29411,28 @@
         <v>0.0496</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1441213553155795</v>
+        <v>0.1466362099203446</v>
       </c>
       <c r="J26" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K26" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L26" t="n">
-        <v>0.02549494368203542</v>
+        <v>0.02656795721511418</v>
       </c>
       <c r="M26" t="n">
-        <v>4.607665236128331</v>
+        <v>4.601790514637037</v>
       </c>
       <c r="N26" t="n">
-        <v>37.08903139650894</v>
+        <v>36.97716718671438</v>
       </c>
       <c r="O26" t="n">
-        <v>6.090076468855621</v>
+        <v>6.080885394966294</v>
       </c>
       <c r="P26" t="n">
-        <v>383.0739528633703</v>
+        <v>383.0441350226789</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -29383,28 +29489,28 @@
         <v>0.0752</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1845094915192203</v>
+        <v>0.1875014331660611</v>
       </c>
       <c r="J27" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K27" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L27" t="n">
-        <v>0.05826700403838447</v>
+        <v>0.06044072927287669</v>
       </c>
       <c r="M27" t="n">
-        <v>3.878099482693387</v>
+        <v>3.878120410362867</v>
       </c>
       <c r="N27" t="n">
-        <v>25.70403474919681</v>
+        <v>25.65118173950459</v>
       </c>
       <c r="O27" t="n">
-        <v>5.069914668827949</v>
+        <v>5.064699570508067</v>
       </c>
       <c r="P27" t="n">
-        <v>366.9918472664395</v>
+        <v>366.9563727546271</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -29461,28 +29567,28 @@
         <v>0.0784</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1710092489078192</v>
+        <v>0.1741549547330035</v>
       </c>
       <c r="J28" t="n">
+        <v>254</v>
+      </c>
+      <c r="K28" t="n">
         <v>253</v>
       </c>
-      <c r="K28" t="n">
-        <v>252</v>
-      </c>
       <c r="L28" t="n">
-        <v>0.03765202214180507</v>
+        <v>0.03926274362572379</v>
       </c>
       <c r="M28" t="n">
-        <v>4.599034515617997</v>
+        <v>4.59437333573655</v>
       </c>
       <c r="N28" t="n">
-        <v>34.8713396392971</v>
+        <v>34.78692522906136</v>
       </c>
       <c r="O28" t="n">
-        <v>5.905195986527213</v>
+        <v>5.898044186767454</v>
       </c>
       <c r="P28" t="n">
-        <v>363.4479997673228</v>
+        <v>363.4106293512211</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -29539,28 +29645,28 @@
         <v>0.1741</v>
       </c>
       <c r="I29" t="n">
-        <v>0.01843949224727162</v>
+        <v>0.02170131820639465</v>
       </c>
       <c r="J29" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K29" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L29" t="n">
-        <v>0.0006003288294751385</v>
+        <v>0.0008366811567995791</v>
       </c>
       <c r="M29" t="n">
-        <v>3.909104911372391</v>
+        <v>3.906625013621674</v>
       </c>
       <c r="N29" t="n">
-        <v>26.47952539792698</v>
+        <v>26.43213805594148</v>
       </c>
       <c r="O29" t="n">
-        <v>5.145826017067326</v>
+        <v>5.141219510577376</v>
       </c>
       <c r="P29" t="n">
-        <v>371.8156521051873</v>
+        <v>371.7769158220804</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -29598,7 +29704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD254"/>
+  <dimension ref="A1:AD255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67805,6 +67911,158 @@
         </is>
       </c>
     </row>
+    <row r="255">
+      <c r="A255" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>-35.631994599085765,174.51512295080857</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>-35.63276879453447,174.51502170315908</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>-35.63334261233594,174.5144235799483</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>-35.633974052902566,174.51391816237623</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>-35.63452136478246,174.513289280044</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>-35.63500516241412,174.51260278064944</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>-35.635519945271355,174.51196505445913</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>-35.636031603076255,174.51132327632274</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>-35.63657048270076,174.5107172953905</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>-35.637116033043675,174.51012020057806</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>-35.63766434436206,174.50952676430006</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>-35.63824666115599,174.50898454031224</t>
+        </is>
+      </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>-35.63880360429648,174.508450530759</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>-35.639409304175565,174.50798446126325</t>
+        </is>
+      </c>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>-35.64003765364312,174.50752492740327</t>
+        </is>
+      </c>
+      <c r="Q255" t="inlineStr">
+        <is>
+          <t>-35.64068638191397,174.50710932137957</t>
+        </is>
+      </c>
+      <c r="R255" t="inlineStr">
+        <is>
+          <t>-35.64131307907751,174.50664274143875</t>
+        </is>
+      </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>-35.64198319513396,174.5062697286053</t>
+        </is>
+      </c>
+      <c r="T255" t="inlineStr">
+        <is>
+          <t>-35.64261902827347,174.50582797994363</t>
+        </is>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>-35.64326791240004,174.50543962179478</t>
+        </is>
+      </c>
+      <c r="V255" t="inlineStr">
+        <is>
+          <t>-35.643907977346515,174.5050463863718</t>
+        </is>
+      </c>
+      <c r="W255" t="inlineStr">
+        <is>
+          <t>-35.6445632700158,174.50465857216358</t>
+        </is>
+      </c>
+      <c r="X255" t="inlineStr">
+        <is>
+          <t>-35.6452189202497,174.50430531277476</t>
+        </is>
+      </c>
+      <c r="Y255" t="inlineStr">
+        <is>
+          <t>-35.645875042465484,174.50395009957364</t>
+        </is>
+      </c>
+      <c r="Z255" t="inlineStr">
+        <is>
+          <t>-35.64657774790703,174.5037104840466</t>
+        </is>
+      </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>-35.64723150179213,174.50327711274542</t>
+        </is>
+      </c>
+      <c r="AB255" t="inlineStr">
+        <is>
+          <t>-35.647909629614325,174.50295755886884</t>
+        </is>
+      </c>
+      <c r="AC255" t="inlineStr">
+        <is>
+          <t>-35.648624030281496,174.5028303599407</t>
+        </is>
+      </c>
+      <c r="AD255" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0094/nzd0094.xlsx
+++ b/data/nzd0094/nzd0094.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD255"/>
+  <dimension ref="A1:AD256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24676,10 +24676,10 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>378.81</v>
+        <v>385.57</v>
       </c>
       <c r="C255" t="n">
-        <v>409.63</v>
+        <v>415.93</v>
       </c>
       <c r="D255" t="n">
         <v>390.26</v>
@@ -24760,6 +24760,102 @@
         <v>376.14</v>
       </c>
       <c r="AD255" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>413.08</v>
+      </c>
+      <c r="C256" t="n">
+        <v>433.4</v>
+      </c>
+      <c r="D256" t="n">
+        <v>390.26</v>
+      </c>
+      <c r="E256" t="n">
+        <v>378.34</v>
+      </c>
+      <c r="F256" t="n">
+        <v>370.82</v>
+      </c>
+      <c r="G256" t="n">
+        <v>364.09</v>
+      </c>
+      <c r="H256" t="n">
+        <v>361.15</v>
+      </c>
+      <c r="I256" t="n">
+        <v>360.44</v>
+      </c>
+      <c r="J256" t="n">
+        <v>361.74</v>
+      </c>
+      <c r="K256" t="n">
+        <v>364.45</v>
+      </c>
+      <c r="L256" t="n">
+        <v>367.35</v>
+      </c>
+      <c r="M256" t="n">
+        <v>374.96</v>
+      </c>
+      <c r="N256" t="n">
+        <v>379.29</v>
+      </c>
+      <c r="O256" t="n">
+        <v>373.99</v>
+      </c>
+      <c r="P256" t="n">
+        <v>371.8</v>
+      </c>
+      <c r="Q256" t="n">
+        <v>371.72</v>
+      </c>
+      <c r="R256" t="n">
+        <v>371.21</v>
+      </c>
+      <c r="S256" t="n">
+        <v>378.47</v>
+      </c>
+      <c r="T256" t="n">
+        <v>382.55</v>
+      </c>
+      <c r="U256" t="n">
+        <v>390</v>
+      </c>
+      <c r="V256" t="n">
+        <v>390.68</v>
+      </c>
+      <c r="W256" t="n">
+        <v>390.46</v>
+      </c>
+      <c r="X256" t="n">
+        <v>392.2</v>
+      </c>
+      <c r="Y256" t="n">
+        <v>384.36</v>
+      </c>
+      <c r="Z256" t="n">
+        <v>388.84</v>
+      </c>
+      <c r="AA256" t="n">
+        <v>374.27</v>
+      </c>
+      <c r="AB256" t="n">
+        <v>372.45</v>
+      </c>
+      <c r="AC256" t="n">
+        <v>377.11</v>
+      </c>
+      <c r="AD256" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -24776,7 +24872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B258"/>
+  <dimension ref="A1:B259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27359,6 +27455,16 @@
       </c>
       <c r="B258" t="n">
         <v>0.17</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>-0.46</v>
       </c>
     </row>
   </sheetData>
@@ -27527,28 +27633,28 @@
         <v>0.0102</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9480261921337116</v>
+        <v>0.9710994336127883</v>
       </c>
       <c r="J2" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K2" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0346939452363505</v>
+        <v>0.03663034981847568</v>
       </c>
       <c r="M2" t="n">
-        <v>26.56946808255524</v>
+        <v>26.51787833124594</v>
       </c>
       <c r="N2" t="n">
-        <v>1099.309630576039</v>
+        <v>1095.320620903897</v>
       </c>
       <c r="O2" t="n">
-        <v>33.15583855938557</v>
+        <v>33.09562842587971</v>
       </c>
       <c r="P2" t="n">
-        <v>369.3833240556464</v>
+        <v>369.0945375169459</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -27609,28 +27715,28 @@
         <v>0.0104</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8779933608934187</v>
+        <v>0.9072043579004853</v>
       </c>
       <c r="J3" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K3" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04584124017162494</v>
+        <v>0.04898478607242152</v>
       </c>
       <c r="M3" t="n">
-        <v>21.9904083584418</v>
+        <v>22.0744169279188</v>
       </c>
       <c r="N3" t="n">
-        <v>752.7795538311881</v>
+        <v>752.8085660363305</v>
       </c>
       <c r="O3" t="n">
-        <v>27.43682842150652</v>
+        <v>27.43735712557481</v>
       </c>
       <c r="P3" t="n">
-        <v>383.5169854877785</v>
+        <v>383.1605459515504</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -27691,28 +27797,28 @@
         <v>0.0106</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3567850162282836</v>
+        <v>0.3562252170367</v>
       </c>
       <c r="J4" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K4" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008368326894605649</v>
+        <v>0.00841609304802815</v>
       </c>
       <c r="M4" t="n">
-        <v>21.11313682051342</v>
+        <v>21.02585815779931</v>
       </c>
       <c r="N4" t="n">
-        <v>672.4701159114309</v>
+        <v>669.6342623625975</v>
       </c>
       <c r="O4" t="n">
-        <v>25.93202876582222</v>
+        <v>25.87729240787369</v>
       </c>
       <c r="P4" t="n">
-        <v>381.3486207726558</v>
+        <v>381.3555615406274</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -27773,28 +27879,28 @@
         <v>0.0239</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8199459392677685</v>
+        <v>0.8222868297112325</v>
       </c>
       <c r="J5" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K5" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08468294725735703</v>
+        <v>0.08579404601740415</v>
       </c>
       <c r="M5" t="n">
-        <v>15.10869722996832</v>
+        <v>15.05936947937661</v>
       </c>
       <c r="N5" t="n">
-        <v>341.2036335295632</v>
+        <v>339.874059482086</v>
       </c>
       <c r="O5" t="n">
-        <v>18.47169817665834</v>
+        <v>18.43567355650685</v>
       </c>
       <c r="P5" t="n">
-        <v>353.6968821082139</v>
+        <v>353.6689199425404</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27851,28 +27957,28 @@
         <v>0.0308</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3581353683282698</v>
+        <v>0.3632786037954847</v>
       </c>
       <c r="J6" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K6" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0283220128357462</v>
+        <v>0.02934552825852066</v>
       </c>
       <c r="M6" t="n">
-        <v>11.72695582223928</v>
+        <v>11.70438965158031</v>
       </c>
       <c r="N6" t="n">
-        <v>201.6881422196574</v>
+        <v>201.0267560616739</v>
       </c>
       <c r="O6" t="n">
-        <v>14.20169504741098</v>
+        <v>14.17839046089766</v>
       </c>
       <c r="P6" t="n">
-        <v>355.298290683938</v>
+        <v>355.236149639493</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27929,28 +28035,28 @@
         <v>0.0359</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2789782646970732</v>
+        <v>0.2822161743253921</v>
       </c>
       <c r="J7" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K7" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02367760851506617</v>
+        <v>0.02441460417680974</v>
       </c>
       <c r="M7" t="n">
-        <v>10.25113288872826</v>
+        <v>10.22217208572892</v>
       </c>
       <c r="N7" t="n">
-        <v>148.2790505990998</v>
+        <v>147.7486380681802</v>
       </c>
       <c r="O7" t="n">
-        <v>12.17698856857063</v>
+        <v>12.15518975862492</v>
       </c>
       <c r="P7" t="n">
-        <v>352.8689022506594</v>
+        <v>352.8299836283933</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28007,28 +28113,28 @@
         <v>0.0369</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1902369316541769</v>
+        <v>0.1928587518887722</v>
       </c>
       <c r="J8" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K8" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01572690152989553</v>
+        <v>0.01628966647287888</v>
       </c>
       <c r="M8" t="n">
-        <v>8.315355297405029</v>
+        <v>8.292858736284995</v>
       </c>
       <c r="N8" t="n">
-        <v>104.6515724995811</v>
+        <v>104.274430759531</v>
       </c>
       <c r="O8" t="n">
-        <v>10.22993511707582</v>
+        <v>10.21148523768854</v>
       </c>
       <c r="P8" t="n">
-        <v>353.0140218155548</v>
+        <v>352.9825083877348</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -28085,28 +28191,28 @@
         <v>0.0422</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2310300965572099</v>
+        <v>0.2324308451460206</v>
       </c>
       <c r="J9" t="n">
+        <v>255</v>
+      </c>
+      <c r="K9" t="n">
         <v>254</v>
       </c>
-      <c r="K9" t="n">
-        <v>253</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.03442765256076918</v>
+        <v>0.03511972184740142</v>
       </c>
       <c r="M9" t="n">
-        <v>6.753985089700988</v>
+        <v>6.733382150377911</v>
       </c>
       <c r="N9" t="n">
-        <v>69.71661467961637</v>
+        <v>69.45266911942335</v>
       </c>
       <c r="O9" t="n">
-        <v>8.349647578168577</v>
+        <v>8.333826799221553</v>
       </c>
       <c r="P9" t="n">
-        <v>352.6244489986059</v>
+        <v>352.6076990906341</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -28163,28 +28269,28 @@
         <v>0.045</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2976769148822173</v>
+        <v>0.2978079100161325</v>
       </c>
       <c r="J10" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K10" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L10" t="n">
-        <v>0.06060724890218316</v>
+        <v>0.06115299220994819</v>
       </c>
       <c r="M10" t="n">
-        <v>6.50881745885988</v>
+        <v>6.48369970215902</v>
       </c>
       <c r="N10" t="n">
-        <v>64.04908880060236</v>
+        <v>63.7960227114162</v>
       </c>
       <c r="O10" t="n">
-        <v>8.00306746195497</v>
+        <v>7.987241245349749</v>
       </c>
       <c r="P10" t="n">
-        <v>353.6397626372006</v>
+        <v>353.6381954424044</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -28241,28 +28347,28 @@
         <v>0.0478</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3516602540246593</v>
+        <v>0.3509657678589425</v>
       </c>
       <c r="J11" t="n">
+        <v>255</v>
+      </c>
+      <c r="K11" t="n">
         <v>254</v>
       </c>
-      <c r="K11" t="n">
-        <v>253</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.09198683278752573</v>
+        <v>0.0923786879520706</v>
       </c>
       <c r="M11" t="n">
-        <v>6.172255156589274</v>
+        <v>6.150948653233783</v>
       </c>
       <c r="N11" t="n">
-        <v>56.85056880738077</v>
+        <v>56.6293359210511</v>
       </c>
       <c r="O11" t="n">
-        <v>7.539931618216492</v>
+        <v>7.525246568787703</v>
       </c>
       <c r="P11" t="n">
-        <v>355.8782151292878</v>
+        <v>355.886519674055</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -28319,28 +28425,28 @@
         <v>0.0536</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2479624285779731</v>
+        <v>0.2453930333382521</v>
       </c>
       <c r="J12" t="n">
+        <v>255</v>
+      </c>
+      <c r="K12" t="n">
         <v>254</v>
       </c>
-      <c r="K12" t="n">
-        <v>253</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.06248007524222898</v>
+        <v>0.06172418795834977</v>
       </c>
       <c r="M12" t="n">
-        <v>5.179727229994197</v>
+        <v>5.170892345354253</v>
       </c>
       <c r="N12" t="n">
-        <v>42.96674831053164</v>
+        <v>42.83301542221779</v>
       </c>
       <c r="O12" t="n">
-        <v>6.554902616403362</v>
+        <v>6.544693684368871</v>
       </c>
       <c r="P12" t="n">
-        <v>363.7511432780834</v>
+        <v>363.7818676594266</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -28397,28 +28503,28 @@
         <v>0.0468</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2420080191724348</v>
+        <v>0.2389754298749426</v>
       </c>
       <c r="J13" t="n">
+        <v>255</v>
+      </c>
+      <c r="K13" t="n">
         <v>254</v>
       </c>
-      <c r="K13" t="n">
-        <v>253</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.06247272453851405</v>
+        <v>0.06144125816413615</v>
       </c>
       <c r="M13" t="n">
-        <v>5.267468114494553</v>
+        <v>5.259159745979696</v>
       </c>
       <c r="N13" t="n">
-        <v>40.9331099185066</v>
+        <v>40.82130812223858</v>
       </c>
       <c r="O13" t="n">
-        <v>6.39789886748037</v>
+        <v>6.38915550931722</v>
       </c>
       <c r="P13" t="n">
-        <v>372.0657551283608</v>
+        <v>372.1020183036763</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -28475,28 +28581,28 @@
         <v>0.0508</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1273284834452958</v>
+        <v>0.1219863130477474</v>
       </c>
       <c r="J14" t="n">
+        <v>255</v>
+      </c>
+      <c r="K14" t="n">
         <v>254</v>
       </c>
-      <c r="K14" t="n">
-        <v>253</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.02261296815312608</v>
+        <v>0.02087513691747656</v>
       </c>
       <c r="M14" t="n">
-        <v>4.674605567032124</v>
+        <v>4.678693305727914</v>
       </c>
       <c r="N14" t="n">
-        <v>32.63487075039418</v>
+        <v>32.6595361663283</v>
       </c>
       <c r="O14" t="n">
-        <v>5.712693826067889</v>
+        <v>5.714852243612979</v>
       </c>
       <c r="P14" t="n">
-        <v>382.169725605813</v>
+        <v>382.2336063501829</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -28553,28 +28659,28 @@
         <v>0.0555</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1177111598986947</v>
+        <v>0.1125957886593762</v>
       </c>
       <c r="J15" t="n">
+        <v>255</v>
+      </c>
+      <c r="K15" t="n">
         <v>254</v>
       </c>
-      <c r="K15" t="n">
-        <v>253</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.01898331320381441</v>
+        <v>0.01747379152966</v>
       </c>
       <c r="M15" t="n">
-        <v>4.694906863921569</v>
+        <v>4.698513942253919</v>
       </c>
       <c r="N15" t="n">
-        <v>33.34735729024792</v>
+        <v>33.35648993361901</v>
       </c>
       <c r="O15" t="n">
-        <v>5.774717074476283</v>
+        <v>5.77550776413806</v>
       </c>
       <c r="P15" t="n">
-        <v>376.8614673918095</v>
+        <v>376.9226361112959</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -28631,28 +28737,28 @@
         <v>0.0487</v>
       </c>
       <c r="I16" t="n">
-        <v>0.006011932274049773</v>
+        <v>0.001018041200342451</v>
       </c>
       <c r="J16" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K16" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L16" t="n">
-        <v>4.024925617407416e-05</v>
+        <v>1.160489805029918e-06</v>
       </c>
       <c r="M16" t="n">
-        <v>5.338343207855274</v>
+        <v>5.336922255967849</v>
       </c>
       <c r="N16" t="n">
-        <v>41.86904706355716</v>
+        <v>41.83723533937064</v>
       </c>
       <c r="O16" t="n">
-        <v>6.470629572426254</v>
+        <v>6.468170942343024</v>
       </c>
       <c r="P16" t="n">
-        <v>377.4903626330483</v>
+        <v>377.5501802194036</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -28709,28 +28815,28 @@
         <v>0.0534</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0382580452739861</v>
+        <v>0.03433895102589848</v>
       </c>
       <c r="J17" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K17" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L17" t="n">
-        <v>0.001543651493357445</v>
+        <v>0.001252416106922283</v>
       </c>
       <c r="M17" t="n">
-        <v>5.214538877341272</v>
+        <v>5.210191430516201</v>
       </c>
       <c r="N17" t="n">
-        <v>44.14338529048617</v>
+        <v>44.05094700727015</v>
       </c>
       <c r="O17" t="n">
-        <v>6.644048862740714</v>
+        <v>6.637088744869255</v>
       </c>
       <c r="P17" t="n">
-        <v>375.2906734411803</v>
+        <v>375.3376169477885</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -28787,28 +28893,28 @@
         <v>0.0579</v>
       </c>
       <c r="I18" t="n">
-        <v>0.05213063008365649</v>
+        <v>0.04688562913816065</v>
       </c>
       <c r="J18" t="n">
+        <v>255</v>
+      </c>
+      <c r="K18" t="n">
         <v>254</v>
       </c>
-      <c r="K18" t="n">
-        <v>253</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.0032249035603924</v>
+        <v>0.00262301400971765</v>
       </c>
       <c r="M18" t="n">
-        <v>5.145051102908715</v>
+        <v>5.144017609995703</v>
       </c>
       <c r="N18" t="n">
-        <v>39.11903728707962</v>
+        <v>39.11265385578751</v>
       </c>
       <c r="O18" t="n">
-        <v>6.254521347559669</v>
+        <v>6.254011021399588</v>
       </c>
       <c r="P18" t="n">
-        <v>375.9790228498068</v>
+        <v>376.0417416587713</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -28865,28 +28971,28 @@
         <v>0.053</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1037286743950108</v>
+        <v>0.1004720331758395</v>
       </c>
       <c r="J19" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K19" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L19" t="n">
-        <v>0.01146978228491347</v>
+        <v>0.0108469240344129</v>
       </c>
       <c r="M19" t="n">
-        <v>5.368360417489096</v>
+        <v>5.361309088893889</v>
       </c>
       <c r="N19" t="n">
-        <v>43.52473534408453</v>
+        <v>43.41155664698206</v>
       </c>
       <c r="O19" t="n">
-        <v>6.597327894237524</v>
+        <v>6.588744694323954</v>
       </c>
       <c r="P19" t="n">
-        <v>379.5497703922748</v>
+        <v>379.58851312774</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -28943,28 +29049,28 @@
         <v>0.049</v>
       </c>
       <c r="I20" t="n">
-        <v>0.07453724047056365</v>
+        <v>0.07091350398038489</v>
       </c>
       <c r="J20" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K20" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L20" t="n">
-        <v>0.006043535978439207</v>
+        <v>0.00551197957323335</v>
       </c>
       <c r="M20" t="n">
-        <v>5.098413267629843</v>
+        <v>5.092928793897526</v>
       </c>
       <c r="N20" t="n">
-        <v>41.88037505524304</v>
+        <v>41.78316599893578</v>
       </c>
       <c r="O20" t="n">
-        <v>6.471504852446843</v>
+        <v>6.46398994421679</v>
       </c>
       <c r="P20" t="n">
-        <v>384.7558359618931</v>
+        <v>384.7996182797995</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -29021,28 +29127,28 @@
         <v>0.0506</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2040623973044895</v>
+        <v>0.2009113996227978</v>
       </c>
       <c r="J21" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K21" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L21" t="n">
-        <v>0.04502444989493792</v>
+        <v>0.04401569770229485</v>
       </c>
       <c r="M21" t="n">
-        <v>4.910325471629938</v>
+        <v>4.903056836534188</v>
       </c>
       <c r="N21" t="n">
-        <v>40.80876497167229</v>
+        <v>40.70018766511808</v>
       </c>
       <c r="O21" t="n">
-        <v>6.388173836995381</v>
+        <v>6.3796698711703</v>
       </c>
       <c r="P21" t="n">
-        <v>388.2320524545929</v>
+        <v>388.2699264234839</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -29099,28 +29205,28 @@
         <v>0.057</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1587735153367046</v>
+        <v>0.1580577396315468</v>
       </c>
       <c r="J22" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K22" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L22" t="n">
-        <v>0.03482853604415814</v>
+        <v>0.03481300472355753</v>
       </c>
       <c r="M22" t="n">
-        <v>4.401454520835079</v>
+        <v>4.38701254079697</v>
       </c>
       <c r="N22" t="n">
-        <v>32.78906873630751</v>
+        <v>32.66326214707538</v>
       </c>
       <c r="O22" t="n">
-        <v>5.726174005067215</v>
+        <v>5.715178225311559</v>
       </c>
       <c r="P22" t="n">
-        <v>387.282795870203</v>
+        <v>387.291311118562</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -29177,28 +29283,28 @@
         <v>0.0611</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1955385354308922</v>
+        <v>0.1954960335723704</v>
       </c>
       <c r="J23" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K23" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L23" t="n">
-        <v>0.05091211970234089</v>
+        <v>0.05131100230860497</v>
       </c>
       <c r="M23" t="n">
-        <v>4.419949279257911</v>
+        <v>4.40279048245338</v>
       </c>
       <c r="N23" t="n">
-        <v>33.45443292917155</v>
+        <v>33.3232488692949</v>
       </c>
       <c r="O23" t="n">
-        <v>5.783980716528328</v>
+        <v>5.772629285628422</v>
       </c>
       <c r="P23" t="n">
-        <v>385.2878402925775</v>
+        <v>385.2883459172842</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -29255,28 +29361,28 @@
         <v>0.064</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2562103584478388</v>
+        <v>0.2575916123081337</v>
       </c>
       <c r="J24" t="n">
+        <v>255</v>
+      </c>
+      <c r="K24" t="n">
         <v>254</v>
       </c>
-      <c r="K24" t="n">
-        <v>253</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.07145669875869087</v>
+        <v>0.07273698699486653</v>
       </c>
       <c r="M24" t="n">
-        <v>5.005480675901071</v>
+        <v>4.991723270101566</v>
       </c>
       <c r="N24" t="n">
-        <v>40.09220654783431</v>
+        <v>39.94474008275032</v>
       </c>
       <c r="O24" t="n">
-        <v>6.331840691918449</v>
+        <v>6.320185130417488</v>
       </c>
       <c r="P24" t="n">
-        <v>383.7238963912124</v>
+        <v>383.7074566460648</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -29333,28 +29439,28 @@
         <v>0.0766</v>
       </c>
       <c r="I25" t="n">
-        <v>0.201332093751014</v>
+        <v>0.2024875751316525</v>
       </c>
       <c r="J25" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K25" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L25" t="n">
-        <v>0.06513119188369676</v>
+        <v>0.06634964699091217</v>
       </c>
       <c r="M25" t="n">
-        <v>4.152327882544828</v>
+        <v>4.141299706749907</v>
       </c>
       <c r="N25" t="n">
-        <v>27.30809294094619</v>
+        <v>27.20824179262455</v>
       </c>
       <c r="O25" t="n">
-        <v>5.225714586632741</v>
+        <v>5.216152010114788</v>
       </c>
       <c r="P25" t="n">
-        <v>377.6155894182664</v>
+        <v>377.601843197405</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -29411,28 +29517,28 @@
         <v>0.0496</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1466362099203446</v>
+        <v>0.1482256284468029</v>
       </c>
       <c r="J26" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K26" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L26" t="n">
-        <v>0.02656795721511418</v>
+        <v>0.02735093558988577</v>
       </c>
       <c r="M26" t="n">
-        <v>4.601790514637037</v>
+        <v>4.59139987939898</v>
       </c>
       <c r="N26" t="n">
-        <v>36.97716718671438</v>
+        <v>36.84585658650093</v>
       </c>
       <c r="O26" t="n">
-        <v>6.080885394966294</v>
+        <v>6.070078795740705</v>
       </c>
       <c r="P26" t="n">
-        <v>383.0441350226789</v>
+        <v>383.0252264548109</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -29489,28 +29595,28 @@
         <v>0.0752</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1875014331660611</v>
+        <v>0.1894514388402857</v>
       </c>
       <c r="J27" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K27" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L27" t="n">
-        <v>0.06044072927287669</v>
+        <v>0.062082245291183</v>
       </c>
       <c r="M27" t="n">
-        <v>3.878120410362867</v>
+        <v>3.872757244196167</v>
       </c>
       <c r="N27" t="n">
-        <v>25.65118173950459</v>
+        <v>25.57120699426272</v>
       </c>
       <c r="O27" t="n">
-        <v>5.064699570508067</v>
+        <v>5.056798097043496</v>
       </c>
       <c r="P27" t="n">
-        <v>366.9563727546271</v>
+        <v>366.9331744503289</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -29567,28 +29673,28 @@
         <v>0.0784</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1741549547330035</v>
+        <v>0.1778713240656229</v>
       </c>
       <c r="J28" t="n">
+        <v>255</v>
+      </c>
+      <c r="K28" t="n">
         <v>254</v>
       </c>
-      <c r="K28" t="n">
-        <v>253</v>
-      </c>
       <c r="L28" t="n">
-        <v>0.03926274362572379</v>
+        <v>0.04114250257147456</v>
       </c>
       <c r="M28" t="n">
-        <v>4.59437333573655</v>
+        <v>4.592047200847765</v>
       </c>
       <c r="N28" t="n">
-        <v>34.78692522906136</v>
+        <v>34.72482008530839</v>
       </c>
       <c r="O28" t="n">
-        <v>5.898044186767454</v>
+        <v>5.892776941757458</v>
       </c>
       <c r="P28" t="n">
-        <v>363.4106293512211</v>
+        <v>363.36633075741</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -29645,28 +29751,28 @@
         <v>0.1741</v>
       </c>
       <c r="I29" t="n">
-        <v>0.02170131820639465</v>
+        <v>0.0257293924431605</v>
       </c>
       <c r="J29" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K29" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L29" t="n">
-        <v>0.0008366811567995791</v>
+        <v>0.001181933820489145</v>
       </c>
       <c r="M29" t="n">
-        <v>3.906625013621674</v>
+        <v>3.907138561917464</v>
       </c>
       <c r="N29" t="n">
-        <v>26.43213805594148</v>
+        <v>26.4159865134633</v>
       </c>
       <c r="O29" t="n">
-        <v>5.141219510577376</v>
+        <v>5.139648481507592</v>
       </c>
       <c r="P29" t="n">
-        <v>371.7769158220804</v>
+        <v>371.728917641992</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -29704,7 +29810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD255"/>
+  <dimension ref="A1:AD256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67919,12 +68025,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>-35.631994599085765,174.51512295080857</t>
+          <t>-35.632021586847735,174.5151898736219</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>-35.63276879453447,174.51502170315908</t>
+          <t>-35.63279394581725,174.51508407267517</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -68058,6 +68164,158 @@
         </is>
       </c>
       <c r="AD255" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>-35.6321314138674,174.51546221824614</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>-35.632863690549065,174.51525702453299</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>-35.63334261233594,174.5144235799483</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>-35.63396003871512,174.51389113068453</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>-35.634494475324956,174.51325119580906</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>-35.634983300415755,174.51257415448072</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>-35.63549297175284,174.511929735317</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>-35.63601639299696,174.51130320667502</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>-35.63655596557228,174.51069794475762</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>-35.637105311968256,174.51010587470898</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>-35.63765581619883,174.50951536868078</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>-35.63823283792709,174.50896516877137</t>
+        </is>
+      </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>-35.63879519037502,174.5084351057677</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>-35.639401248584086,174.5079656956336</t>
+        </is>
+      </c>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>-35.64003459082296,174.5075177925084</t>
+        </is>
+      </c>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <t>-35.64067782227707,174.50709000897515</t>
+        </is>
+      </c>
+      <c r="R256" t="inlineStr">
+        <is>
+          <t>-35.64131033641454,174.50663690291478</t>
+        </is>
+      </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>-35.641969026081355,174.50624034996773</t>
+        </is>
+      </c>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>-35.64261228762655,174.50581400360664</t>
+        </is>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>-35.64326173964158,174.50542550708627</t>
+        </is>
+      </c>
+      <c r="V256" t="inlineStr">
+        <is>
+          <t>-35.64390560446593,174.505040187203</t>
+        </is>
+      </c>
+      <c r="W256" t="inlineStr">
+        <is>
+          <t>-35.64456334467807,174.5046587732036</t>
+        </is>
+      </c>
+      <c r="X256" t="inlineStr">
+        <is>
+          <t>-35.64521783341867,174.50430192032758</t>
+        </is>
+      </c>
+      <c r="Y256" t="inlineStr">
+        <is>
+          <t>-35.645870634753294,174.503933507145</t>
+        </is>
+      </c>
+      <c r="Z256" t="inlineStr">
+        <is>
+          <t>-35.64657493078684,174.5036996451779</t>
+        </is>
+      </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>-35.64722832908076,174.50326490577564</t>
+        </is>
+      </c>
+      <c r="AB256" t="inlineStr">
+        <is>
+          <t>-35.647911291902375,174.50296558757557</t>
+        </is>
+      </c>
+      <c r="AC256" t="inlineStr">
+        <is>
+          <t>-35.64862566662901,174.50284088342258</t>
+        </is>
+      </c>
+      <c r="AD256" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
